--- a/Finanzas Personales.xlsx
+++ b/Finanzas Personales.xlsx
@@ -177,9 +177,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -212,9 +212,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -35001,7 +35001,7 @@
         <v>46023</v>
       </c>
       <c r="C2" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D2" t="str">
         <v>Bonificación Ahorro</v>
@@ -35024,7 +35024,7 @@
         <v>46023</v>
       </c>
       <c r="C3" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D3" t="str">
         <v>Pago de Tarjeta BBVA Bfree</v>
@@ -35047,7 +35047,7 @@
         <v>46023</v>
       </c>
       <c r="C4" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D4" t="str">
         <v>Linea Tarjeta</v>
@@ -35070,7 +35070,7 @@
         <v>46023</v>
       </c>
       <c r="C5" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D5" t="str">
         <v>Comida</v>
@@ -35093,7 +35093,7 @@
         <v>46023</v>
       </c>
       <c r="C6" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D6" t="str">
         <v>Taxi</v>
@@ -35116,7 +35116,7 @@
         <v>46023</v>
       </c>
       <c r="C7" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D7" t="str">
         <v>Salida Familiar</v>
@@ -35139,7 +35139,7 @@
         <v>46023</v>
       </c>
       <c r="C8" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D8" t="str">
         <v>Chifa</v>
@@ -35162,7 +35162,7 @@
         <v>46023</v>
       </c>
       <c r="C9" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D9" t="str">
         <v>Gaseosa</v>
@@ -35185,7 +35185,7 @@
         <v>46023</v>
       </c>
       <c r="C10" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D10" t="str">
         <v>Broaster</v>
@@ -35208,7 +35208,7 @@
         <v>46023</v>
       </c>
       <c r="C11" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D11" t="str">
         <v>Chupete</v>
@@ -35231,7 +35231,7 @@
         <v>46023</v>
       </c>
       <c r="C12" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D12" t="str">
         <v>Bus</v>
@@ -35254,7 +35254,7 @@
         <v>46023</v>
       </c>
       <c r="C13" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D13" t="str">
         <v>Sueldo</v>
@@ -35277,7 +35277,7 @@
         <v>46023</v>
       </c>
       <c r="C14" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D14" t="str">
         <v>Concierto Bad Bunny</v>
@@ -35300,7 +35300,7 @@
         <v>46023</v>
       </c>
       <c r="C15" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D15" t="str">
         <v>Broaster</v>
@@ -35323,7 +35323,7 @@
         <v>46023</v>
       </c>
       <c r="C16" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D16" t="str">
         <v>Condones</v>
@@ -35346,7 +35346,7 @@
         <v>46023</v>
       </c>
       <c r="C17" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D17" t="str">
         <v>Turron</v>
@@ -35369,7 +35369,7 @@
         <v>46023</v>
       </c>
       <c r="C18" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D18" t="str">
         <v>Spotify</v>
@@ -35392,7 +35392,7 @@
         <v>46023</v>
       </c>
       <c r="C19" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D19" t="str">
         <v>Internet</v>
@@ -35415,7 +35415,7 @@
         <v>46023</v>
       </c>
       <c r="C20" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D20" t="str">
         <v>Luz</v>
@@ -35438,7 +35438,7 @@
         <v>46023</v>
       </c>
       <c r="C21" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D21" t="str">
         <v>Gas</v>
@@ -35461,7 +35461,7 @@
         <v>46023</v>
       </c>
       <c r="C22" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D22" t="str">
         <v>Agua + Mantenimiento</v>
@@ -35484,7 +35484,7 @@
         <v>46023</v>
       </c>
       <c r="C23" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D23" t="str">
         <v>Comida</v>
@@ -35507,7 +35507,7 @@
         <v>46023</v>
       </c>
       <c r="C24" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D24" t="str">
         <v>IA</v>
@@ -35530,7 +35530,7 @@
         <v>46023</v>
       </c>
       <c r="C25" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D25" t="str">
         <v>Corte de Cabello</v>
@@ -35553,7 +35553,7 @@
         <v>46024</v>
       </c>
       <c r="C26" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D26" t="str">
         <v>Cumpleaños Fatima</v>
@@ -35576,7 +35576,7 @@
         <v>46024</v>
       </c>
       <c r="C27" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D27" t="str">
         <v>Broaster</v>
@@ -35599,7 +35599,7 @@
         <v>46026</v>
       </c>
       <c r="C28" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D28" t="str">
         <v>Cumpleaños</v>
@@ -35622,7 +35622,7 @@
         <v>46026</v>
       </c>
       <c r="C29" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D29" t="str">
         <v>Cumpleaños</v>
@@ -35645,7 +35645,7 @@
         <v>46026</v>
       </c>
       <c r="C30" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D30" t="str">
         <v>Pollo a la Brasa</v>
@@ -35668,7 +35668,7 @@
         <v>46027</v>
       </c>
       <c r="C31" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D31" t="str">
         <v>Madre</v>
@@ -35691,7 +35691,7 @@
         <v>46028</v>
       </c>
       <c r="C32" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D32" t="str">
         <v>Cumpleaños Fatima</v>
@@ -35714,7 +35714,7 @@
         <v>46028</v>
       </c>
       <c r="C33" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D33" t="str">
         <v>Taxi</v>
@@ -35737,7 +35737,7 @@
         <v>46028</v>
       </c>
       <c r="C34" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D34" t="str">
         <v>Gaseosa</v>
@@ -35760,7 +35760,7 @@
         <v>46028</v>
       </c>
       <c r="C35" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D35" t="str">
         <v>Broaster</v>
@@ -35783,7 +35783,7 @@
         <v>46030</v>
       </c>
       <c r="C36" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D36" t="str">
         <v>Broaster</v>
@@ -35806,7 +35806,7 @@
         <v>46032</v>
       </c>
       <c r="C37" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D37" t="str">
         <v>Desvagramen</v>
@@ -35829,7 +35829,7 @@
         <v>46032</v>
       </c>
       <c r="C38" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D38" t="str">
         <v>Broaster</v>
@@ -35852,7 +35852,7 @@
         <v>46033</v>
       </c>
       <c r="C39" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D39" t="str">
         <v>Shawarma</v>
@@ -35875,7 +35875,7 @@
         <v>46033</v>
       </c>
       <c r="C40" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D40" t="str">
         <v>Alcohol</v>
@@ -35898,7 +35898,7 @@
         <v>46033</v>
       </c>
       <c r="C41" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D41" t="str">
         <v>Broaster</v>
@@ -35921,7 +35921,7 @@
         <v>46034</v>
       </c>
       <c r="C42" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D42" t="str">
         <v>Broaster</v>
@@ -35944,7 +35944,7 @@
         <v>46035</v>
       </c>
       <c r="C43" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D43" t="str">
         <v>Camisa</v>
@@ -35967,7 +35967,7 @@
         <v>46036</v>
       </c>
       <c r="C44" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D44" t="str">
         <v>iCloud</v>
@@ -35990,7 +35990,7 @@
         <v>46036</v>
       </c>
       <c r="C45" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D45" t="str">
         <v>Broaster</v>
@@ -36013,7 +36013,7 @@
         <v>46037</v>
       </c>
       <c r="C46" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D46" t="str">
         <v>Telefonia Movil</v>
@@ -36036,7 +36036,7 @@
         <v>46037</v>
       </c>
       <c r="C47" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D47" t="str">
         <v>Yape Crédito</v>
@@ -36059,7 +36059,7 @@
         <v>46037</v>
       </c>
       <c r="C48" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D48" t="str">
         <v>Shawarma</v>
@@ -36082,7 +36082,7 @@
         <v>46039</v>
       </c>
       <c r="C49" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D49" t="str">
         <v>Gorra</v>
@@ -36105,7 +36105,7 @@
         <v>46039</v>
       </c>
       <c r="C50" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D50" t="str">
         <v>Taxi</v>
@@ -36128,7 +36128,7 @@
         <v>46039</v>
       </c>
       <c r="C51" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D51" t="str">
         <v>Cerveza</v>
@@ -36151,7 +36151,7 @@
         <v>46039</v>
       </c>
       <c r="C52" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D52" t="str">
         <v>Broaster</v>
@@ -36174,7 +36174,7 @@
         <v>46039</v>
       </c>
       <c r="C53" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D53" t="str">
         <v>Cerveza</v>
@@ -36197,7 +36197,7 @@
         <v>46039</v>
       </c>
       <c r="C54" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D54" t="str">
         <v>Bus</v>
@@ -36220,7 +36220,7 @@
         <v>46039</v>
       </c>
       <c r="C55" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Gasto</v>
       </c>
       <c r="D55" t="str">
         <v>Videojuegos</v>
@@ -36243,7 +36243,7 @@
         <v>46039</v>
       </c>
       <c r="C56" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D56" t="str">
         <v>Makis</v>
@@ -36266,7 +36266,7 @@
         <v>46039</v>
       </c>
       <c r="C57" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D57" t="str">
         <v>Gaseosa</v>
@@ -36289,7 +36289,7 @@
         <v>46039</v>
       </c>
       <c r="C58" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D58" t="str">
         <v>Gaseosa</v>
@@ -36312,7 +36312,7 @@
         <v>46041</v>
       </c>
       <c r="C59" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D59" t="str">
         <v>Futbol</v>
@@ -36335,7 +36335,7 @@
         <v>46043</v>
       </c>
       <c r="C60" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D60" t="str">
         <v>Tacos</v>
@@ -36358,7 +36358,7 @@
         <v>46043</v>
       </c>
       <c r="C61" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D61" t="str">
         <v>Bus</v>
@@ -36381,7 +36381,7 @@
         <v>46043</v>
       </c>
       <c r="C62" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D62" t="str">
         <v>FourLoko</v>
@@ -36404,7 +36404,7 @@
         <v>46044</v>
       </c>
       <c r="C63" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D63" t="str">
         <v>Gaseosa</v>
@@ -36427,7 +36427,7 @@
         <v>46044</v>
       </c>
       <c r="C64" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D64" t="str">
         <v>Bus</v>
@@ -36450,7 +36450,7 @@
         <v>46044</v>
       </c>
       <c r="C65" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D65" t="str">
         <v>Bus</v>
@@ -36473,7 +36473,7 @@
         <v>46044</v>
       </c>
       <c r="C66" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D66" t="str">
         <v>Futbol</v>
@@ -36496,7 +36496,7 @@
         <v>46045</v>
       </c>
       <c r="C67" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D67" t="str">
         <v>Futbol</v>
@@ -36519,7 +36519,7 @@
         <v>46045</v>
       </c>
       <c r="C68" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D68" t="str">
         <v>Broaster</v>
@@ -36542,7 +36542,7 @@
         <v>46047</v>
       </c>
       <c r="C69" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D69" t="str">
         <v>Mercado</v>
@@ -36565,7 +36565,7 @@
         <v>46054</v>
       </c>
       <c r="C70" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D70" t="str">
         <v>Broaster</v>
@@ -36588,7 +36588,7 @@
         <v>46054</v>
       </c>
       <c r="C71" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D71" t="str">
         <v>Bonificación Ahorro</v>
@@ -36611,7 +36611,7 @@
         <v>46054</v>
       </c>
       <c r="C72" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D72" t="str">
         <v>Sueldo</v>
@@ -36634,7 +36634,7 @@
         <v>46054</v>
       </c>
       <c r="C73" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D73" t="str">
         <v>Pago de Tarjeta BBVA Bfree</v>
@@ -36657,7 +36657,7 @@
         <v>46054</v>
       </c>
       <c r="C74" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D74" t="str">
         <v>Linea Tarjeta</v>
@@ -36680,7 +36680,7 @@
         <v>46054</v>
       </c>
       <c r="C75" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D75" t="str">
         <v>Internet</v>
@@ -36703,7 +36703,7 @@
         <v>46054</v>
       </c>
       <c r="C76" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D76" t="str">
         <v>Luz</v>
@@ -36726,7 +36726,7 @@
         <v>46054</v>
       </c>
       <c r="C77" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D77" t="str">
         <v>Gas</v>
@@ -36749,7 +36749,7 @@
         <v>46054</v>
       </c>
       <c r="C78" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D78" t="str">
         <v>Corte de Cabello</v>
@@ -36772,7 +36772,7 @@
         <v>46054</v>
       </c>
       <c r="C79" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D79" t="str">
         <v>Agua + Mantenimiento</v>
@@ -36795,7 +36795,7 @@
         <v>46054</v>
       </c>
       <c r="C80" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D80" t="str">
         <v>Viaje Argentina</v>
@@ -36818,7 +36818,7 @@
         <v>46054</v>
       </c>
       <c r="C81" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D81" t="str">
         <v>Condones</v>
@@ -36841,7 +36841,7 @@
         <v>46054</v>
       </c>
       <c r="C82" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D82" t="str">
         <v>Broaster</v>
@@ -36864,7 +36864,7 @@
         <v>46054</v>
       </c>
       <c r="C83" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D83" t="str">
         <v>Mercado</v>
@@ -36887,7 +36887,7 @@
         <v>46054</v>
       </c>
       <c r="C84" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D84" t="str">
         <v>Utencilios de Limpieza</v>
@@ -36910,7 +36910,7 @@
         <v>46054</v>
       </c>
       <c r="C85" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D85" t="str">
         <v>Papa Rellena</v>
@@ -36933,7 +36933,7 @@
         <v>46054</v>
       </c>
       <c r="C86" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D86" t="str">
         <v>Pasaporte</v>
@@ -36956,7 +36956,7 @@
         <v>46054</v>
       </c>
       <c r="C87" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D87" t="str">
         <v>Broaster</v>
@@ -36979,7 +36979,7 @@
         <v>46054</v>
       </c>
       <c r="C88" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D88" t="str">
         <v>Menú</v>
@@ -37002,7 +37002,7 @@
         <v>46054</v>
       </c>
       <c r="C89" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D89" t="str">
         <v>Broaster</v>
@@ -37025,7 +37025,7 @@
         <v>46054</v>
       </c>
       <c r="C90" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D90" t="str">
         <v>Utencilios de Limpieza</v>
@@ -37048,7 +37048,7 @@
         <v>46054</v>
       </c>
       <c r="C91" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D91" t="str">
         <v>Bus</v>
@@ -37071,7 +37071,7 @@
         <v>46054</v>
       </c>
       <c r="C92" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D92" t="str">
         <v>Empanada</v>
@@ -37094,7 +37094,7 @@
         <v>46054</v>
       </c>
       <c r="C93" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D93" t="str">
         <v>DNI Electronico</v>
@@ -37117,7 +37117,7 @@
         <v>46054</v>
       </c>
       <c r="C94" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D94" t="str">
         <v>Bus</v>
@@ -37140,7 +37140,7 @@
         <v>46054</v>
       </c>
       <c r="C95" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D95" t="str">
         <v>Agua Mineral</v>
@@ -37163,7 +37163,7 @@
         <v>46054</v>
       </c>
       <c r="C96" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D96" t="str">
         <v>Gaseosa</v>
@@ -37186,7 +37186,7 @@
         <v>46054</v>
       </c>
       <c r="C97" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D97" t="str">
         <v>Chicharron</v>
@@ -37209,7 +37209,7 @@
         <v>46054</v>
       </c>
       <c r="C98" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D98" t="str">
         <v>Chifa</v>
@@ -37232,7 +37232,7 @@
         <v>46054</v>
       </c>
       <c r="C99" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D99" t="str">
         <v>Propina</v>
@@ -37255,7 +37255,7 @@
         <v>46054</v>
       </c>
       <c r="C100" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D100" t="str">
         <v>Gaseosa</v>
@@ -37278,7 +37278,7 @@
         <v>46054</v>
       </c>
       <c r="C101" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D101" t="str">
         <v>Spotify</v>
@@ -37301,7 +37301,7 @@
         <v>46055</v>
       </c>
       <c r="C102" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D102" t="str">
         <v>Mercado</v>
@@ -37324,7 +37324,7 @@
         <v>46055</v>
       </c>
       <c r="C103" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D103" t="str">
         <v>Condones</v>
@@ -37347,7 +37347,7 @@
         <v>46055</v>
       </c>
       <c r="C104" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D104" t="str">
         <v>Broaster</v>
@@ -37370,7 +37370,7 @@
         <v>46057</v>
       </c>
       <c r="C105" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D105" t="str">
         <v>Utencilios de Aseo Personal</v>
@@ -37393,7 +37393,7 @@
         <v>46057</v>
       </c>
       <c r="C106" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D106" t="str">
         <v>Utencilios de Limpieza</v>
@@ -37416,7 +37416,7 @@
         <v>46057</v>
       </c>
       <c r="C107" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D107" t="str">
         <v>Menú</v>
@@ -37439,7 +37439,7 @@
         <v>46057</v>
       </c>
       <c r="C108" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D108" t="str">
         <v>Temu</v>
@@ -37462,7 +37462,7 @@
         <v>46058</v>
       </c>
       <c r="C109" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D109" t="str">
         <v>Mercado</v>
@@ -37485,7 +37485,7 @@
         <v>46059</v>
       </c>
       <c r="C110" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D110" t="str">
         <v>Futbol</v>
@@ -37508,7 +37508,7 @@
         <v>46059</v>
       </c>
       <c r="C111" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D111" t="str">
         <v>Desvagramen</v>
@@ -37531,7 +37531,7 @@
         <v>46059</v>
       </c>
       <c r="C112" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D112" t="str">
         <v>AFP</v>
@@ -37554,7 +37554,7 @@
         <v>46059</v>
       </c>
       <c r="C113" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D113" t="str">
         <v>Viaje Argentina</v>
@@ -37577,7 +37577,7 @@
         <v>46059</v>
       </c>
       <c r="C114" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D114" t="str">
         <v>Viaje Argentina</v>
@@ -37600,7 +37600,7 @@
         <v>46059</v>
       </c>
       <c r="C115" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D115" t="str">
         <v>AFP</v>
@@ -37623,7 +37623,7 @@
         <v>46059</v>
       </c>
       <c r="C116" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D116" t="str">
         <v>Gaseosa</v>
@@ -37646,7 +37646,7 @@
         <v>46060</v>
       </c>
       <c r="C117" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D117" t="str">
         <v>Dulce de Leche</v>
@@ -37669,7 +37669,7 @@
         <v>46060</v>
       </c>
       <c r="C118" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D118" t="str">
         <v>Gaseosa</v>
@@ -37692,7 +37692,7 @@
         <v>46060</v>
       </c>
       <c r="C119" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D119" t="str">
         <v>Broaster</v>
@@ -37715,7 +37715,7 @@
         <v>46060</v>
       </c>
       <c r="C120" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D120" t="str">
         <v>Gaseosa</v>
@@ -37738,7 +37738,7 @@
         <v>46060</v>
       </c>
       <c r="C121" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D121" t="str">
         <v>Broaster</v>
@@ -37761,7 +37761,7 @@
         <v>46062</v>
       </c>
       <c r="C122" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D122" t="str">
         <v>Broaster</v>
@@ -37784,7 +37784,7 @@
         <v>46063</v>
       </c>
       <c r="C123" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D123" t="str">
         <v>Linea Tarjeta</v>
@@ -37807,7 +37807,7 @@
         <v>46063</v>
       </c>
       <c r="C124" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D124" t="str">
         <v>Condones</v>
@@ -37830,7 +37830,7 @@
         <v>46063</v>
       </c>
       <c r="C125" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D125" t="str">
         <v>Bus</v>
@@ -37853,7 +37853,7 @@
         <v>46063</v>
       </c>
       <c r="C126" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D126" t="str">
         <v>Broaster</v>
@@ -37876,7 +37876,7 @@
         <v>46064</v>
       </c>
       <c r="C127" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D127" t="str">
         <v>Taxi</v>
@@ -37899,7 +37899,7 @@
         <v>46064</v>
       </c>
       <c r="C128" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D128" t="str">
         <v>Dulce</v>
@@ -37922,7 +37922,7 @@
         <v>46064</v>
       </c>
       <c r="C129" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D129" t="str">
         <v>Polo</v>
@@ -37945,7 +37945,7 @@
         <v>46064</v>
       </c>
       <c r="C130" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D130" t="str">
         <v>Gorra</v>
@@ -37968,7 +37968,7 @@
         <v>46064</v>
       </c>
       <c r="C131" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D131" t="str">
         <v>Arreglar Zapatillas</v>
@@ -37991,7 +37991,7 @@
         <v>46064</v>
       </c>
       <c r="C132" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D132" t="str">
         <v>Makis</v>
@@ -38014,7 +38014,7 @@
         <v>46065</v>
       </c>
       <c r="C133" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D133" t="str">
         <v>Camisa</v>
@@ -38037,7 +38037,7 @@
         <v>46066</v>
       </c>
       <c r="C134" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D134" t="str">
         <v>Madre</v>
@@ -38060,7 +38060,7 @@
         <v>46066</v>
       </c>
       <c r="C135" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D135" t="str">
         <v>Salida Casual</v>
@@ -38083,7 +38083,7 @@
         <v>46067</v>
       </c>
       <c r="C136" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D136" t="str">
         <v>Yogurt</v>
@@ -38106,7 +38106,7 @@
         <v>46067</v>
       </c>
       <c r="C137" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D137" t="str">
         <v>Venta de iPhone</v>
@@ -38129,7 +38129,7 @@
         <v>46067</v>
       </c>
       <c r="C138" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D138" t="str">
         <v>iCloud</v>
@@ -38152,7 +38152,7 @@
         <v>46067</v>
       </c>
       <c r="C139" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D139" t="str">
         <v>Polo y/o Camisa</v>
@@ -38175,7 +38175,7 @@
         <v>46067</v>
       </c>
       <c r="C140" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D140" t="str">
         <v>Broaster</v>
@@ -38198,7 +38198,7 @@
         <v>46067</v>
       </c>
       <c r="C141" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D141" t="str">
         <v>Utencilios de Aseo Personal</v>
@@ -38221,7 +38221,7 @@
         <v>46068</v>
       </c>
       <c r="C142" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D142" t="str">
         <v>Telefonia Movil</v>
@@ -38244,7 +38244,7 @@
         <v>46068</v>
       </c>
       <c r="C143" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D143" t="str">
         <v>Yape Crédito</v>
@@ -38267,7 +38267,7 @@
         <v>46068</v>
       </c>
       <c r="C144" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D144" t="str">
         <v>Salida Casual</v>
@@ -38290,7 +38290,7 @@
         <v>46068</v>
       </c>
       <c r="C145" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D145" t="str">
         <v>Gaseosa</v>
@@ -38313,7 +38313,7 @@
         <v>46069</v>
       </c>
       <c r="C146" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D146" t="str">
         <v>Mercado</v>
@@ -38336,7 +38336,7 @@
         <v>46069</v>
       </c>
       <c r="C147" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D147" t="str">
         <v>Futbol</v>
@@ -38359,7 +38359,7 @@
         <v>46069</v>
       </c>
       <c r="C148" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D148" t="str">
         <v>Broaster</v>
@@ -38382,7 +38382,7 @@
         <v>46071</v>
       </c>
       <c r="C149" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D149" t="str">
         <v>Broaster</v>
@@ -38405,7 +38405,7 @@
         <v>46072</v>
       </c>
       <c r="C150" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D150" t="str">
         <v>Bus</v>
@@ -38428,7 +38428,7 @@
         <v>46072</v>
       </c>
       <c r="C151" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D151" t="str">
         <v>Broaster</v>
@@ -38451,7 +38451,7 @@
         <v>46073</v>
       </c>
       <c r="C152" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D152" t="str">
         <v>Concierto Paulo Londra</v>
@@ -38474,7 +38474,7 @@
         <v>46073</v>
       </c>
       <c r="C153" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D153" t="str">
         <v>Mili</v>
@@ -38497,7 +38497,7 @@
         <v>46073</v>
       </c>
       <c r="C154" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D154" t="str">
         <v>Gaseosa</v>
@@ -38520,7 +38520,7 @@
         <v>46073</v>
       </c>
       <c r="C155" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D155" t="str">
         <v>Taxi</v>
@@ -38543,7 +38543,7 @@
         <v>46074</v>
       </c>
       <c r="C156" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D156" t="str">
         <v>Pollo a la Brasa</v>
@@ -38566,7 +38566,7 @@
         <v>46074</v>
       </c>
       <c r="C157" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D157" t="str">
         <v>Madre</v>
@@ -38589,7 +38589,7 @@
         <v>46074</v>
       </c>
       <c r="C158" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D158" t="str">
         <v>Broaster</v>
@@ -38612,7 +38612,7 @@
         <v>46074</v>
       </c>
       <c r="C159" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D159" t="str">
         <v>Alcohol</v>
@@ -38635,7 +38635,7 @@
         <v>46074</v>
       </c>
       <c r="C160" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D160" t="str">
         <v>Agua Mineral</v>
@@ -38658,7 +38658,7 @@
         <v>46074</v>
       </c>
       <c r="C161" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D161" t="str">
         <v>Cigarro</v>
@@ -38681,7 +38681,7 @@
         <v>46074</v>
       </c>
       <c r="C162" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D162" t="str">
         <v>Chifa</v>
@@ -38704,7 +38704,7 @@
         <v>46074</v>
       </c>
       <c r="C163" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D163" t="str">
         <v>Cigarro</v>
@@ -38727,7 +38727,7 @@
         <v>46074</v>
       </c>
       <c r="C164" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D164" t="str">
         <v>Cigarro</v>
@@ -38750,7 +38750,7 @@
         <v>46075</v>
       </c>
       <c r="C165" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D165" t="str">
         <v>Ceviche</v>
@@ -38773,7 +38773,7 @@
         <v>46075</v>
       </c>
       <c r="C166" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D166" t="str">
         <v>Chicharron</v>
@@ -38796,7 +38796,7 @@
         <v>46075</v>
       </c>
       <c r="C167" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D167" t="str">
         <v>Shawarma</v>
@@ -38819,7 +38819,7 @@
         <v>46075</v>
       </c>
       <c r="C168" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D168" t="str">
         <v>Bus</v>
@@ -38842,7 +38842,7 @@
         <v>46075</v>
       </c>
       <c r="C169" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D169" t="str">
         <v>Desvagramen</v>
@@ -38865,7 +38865,7 @@
         <v>46077</v>
       </c>
       <c r="C170" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D170" t="str">
         <v>Pollo a la Brasa</v>
@@ -38888,7 +38888,7 @@
         <v>46077</v>
       </c>
       <c r="C171" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D171" t="str">
         <v>Pago de Tarjeta BBVA Bfree</v>
@@ -38911,7 +38911,7 @@
         <v>46077</v>
       </c>
       <c r="C172" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D172" t="str">
         <v>Linea Tarjeta</v>
@@ -38934,7 +38934,7 @@
         <v>46078</v>
       </c>
       <c r="C173" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D173" t="str">
         <v>Broaster</v>
@@ -38957,7 +38957,7 @@
         <v>46078</v>
       </c>
       <c r="C174" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D174" t="str">
         <v>Dulce de Leche</v>
@@ -38980,7 +38980,7 @@
         <v>46082</v>
       </c>
       <c r="C175" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D175" t="str">
         <v>Bonificación Ahorro</v>
@@ -39003,7 +39003,7 @@
         <v>46082</v>
       </c>
       <c r="C176" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D176" t="str">
         <v>Sueldo</v>
@@ -39026,7 +39026,7 @@
         <v>46082</v>
       </c>
       <c r="C177" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D177" t="str">
         <v>Linea Tarjeta</v>
@@ -39049,7 +39049,7 @@
         <v>46082</v>
       </c>
       <c r="C178" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D178" t="str">
         <v>Internet</v>
@@ -39072,7 +39072,7 @@
         <v>46082</v>
       </c>
       <c r="C179" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D179" t="str">
         <v>Luz</v>
@@ -39095,7 +39095,7 @@
         <v>46082</v>
       </c>
       <c r="C180" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D180" t="str">
         <v>Gas</v>
@@ -39118,7 +39118,7 @@
         <v>46082</v>
       </c>
       <c r="C181" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D181" t="str">
         <v>Viaje Argentina</v>
@@ -39141,7 +39141,7 @@
         <v>46082</v>
       </c>
       <c r="C182" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D182" t="str">
         <v>Viaje Argentina</v>
@@ -39164,7 +39164,7 @@
         <v>46082</v>
       </c>
       <c r="C183" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D183" t="str">
         <v>Concierto Rawayana</v>
@@ -39187,7 +39187,7 @@
         <v>46082</v>
       </c>
       <c r="C184" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D184" t="str">
         <v>Concierto Milo J</v>
@@ -39210,7 +39210,7 @@
         <v>46082</v>
       </c>
       <c r="C185" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D185" t="str">
         <v>Corte de Cabello</v>
@@ -39233,7 +39233,7 @@
         <v>46082</v>
       </c>
       <c r="C186" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D186" t="str">
         <v>Agua + Mantenimiento</v>
@@ -39256,7 +39256,7 @@
         <v>46082</v>
       </c>
       <c r="C187" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D187" t="str">
         <v>Shawarma</v>
@@ -39279,7 +39279,7 @@
         <v>46082</v>
       </c>
       <c r="C188" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D188" t="str">
         <v>Aaron</v>
@@ -39302,7 +39302,7 @@
         <v>46082</v>
       </c>
       <c r="C189" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D189" t="str">
         <v>Maleta</v>
@@ -39325,7 +39325,7 @@
         <v>46082</v>
       </c>
       <c r="C190" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D190" t="str">
         <v>Cumpleaños Abuela</v>
@@ -39348,7 +39348,7 @@
         <v>46082</v>
       </c>
       <c r="C191" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D191" t="str">
         <v>Pantalon</v>
@@ -39371,7 +39371,7 @@
         <v>46082</v>
       </c>
       <c r="C192" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D192" t="str">
         <v>Taxi</v>
@@ -39394,7 +39394,7 @@
         <v>46082</v>
       </c>
       <c r="C193" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D193" t="str">
         <v>Polo</v>
@@ -39417,7 +39417,7 @@
         <v>46082</v>
       </c>
       <c r="C194" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D194" t="str">
         <v>Camisa</v>
@@ -39440,7 +39440,7 @@
         <v>46082</v>
       </c>
       <c r="C195" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D195" t="str">
         <v>Café</v>
@@ -39463,7 +39463,7 @@
         <v>46082</v>
       </c>
       <c r="C196" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D196" t="str">
         <v>Agua Mineral</v>
@@ -39486,7 +39486,7 @@
         <v>46082</v>
       </c>
       <c r="C197" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D197" t="str">
         <v>Broaster</v>
@@ -39509,7 +39509,7 @@
         <v>46082</v>
       </c>
       <c r="C198" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D198" t="str">
         <v>Broaster</v>
@@ -39532,7 +39532,7 @@
         <v>46082</v>
       </c>
       <c r="C199" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D199" t="str">
         <v>Mercado</v>
@@ -39555,7 +39555,7 @@
         <v>46082</v>
       </c>
       <c r="C200" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D200" t="str">
         <v>Spotify</v>
@@ -39578,7 +39578,7 @@
         <v>46083</v>
       </c>
       <c r="C201" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D201" t="str">
         <v>Streaming</v>
@@ -39601,7 +39601,7 @@
         <v>46084</v>
       </c>
       <c r="C202" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D202" t="str">
         <v>Utencilios de Limpieza</v>
@@ -39624,7 +39624,7 @@
         <v>46084</v>
       </c>
       <c r="C203" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D203" t="str">
         <v>Utencilios de Aseo Personal</v>
@@ -39647,7 +39647,7 @@
         <v>46084</v>
       </c>
       <c r="C204" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D204" t="str">
         <v>Pollo a la Brasa</v>
@@ -39670,7 +39670,7 @@
         <v>46084</v>
       </c>
       <c r="C205" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D205" t="str">
         <v>Dollarcity</v>
@@ -39693,7 +39693,7 @@
         <v>46085</v>
       </c>
       <c r="C206" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D206" t="str">
         <v>Zapatillas</v>
@@ -39716,7 +39716,7 @@
         <v>46085</v>
       </c>
       <c r="C207" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D207" t="str">
         <v>Broaster</v>
@@ -39739,7 +39739,7 @@
         <v>46085</v>
       </c>
       <c r="C208" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D208" t="str">
         <v>Gaseosa</v>
@@ -39762,7 +39762,7 @@
         <v>46086</v>
       </c>
       <c r="C209" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D209" t="str">
         <v>Galleta Casino</v>
@@ -39785,7 +39785,7 @@
         <v>46086</v>
       </c>
       <c r="C210" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D210" t="str">
         <v>Arreglar Abrigo</v>
@@ -39808,7 +39808,7 @@
         <v>46087</v>
       </c>
       <c r="C211" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D211" t="str">
         <v>Madre</v>
@@ -39831,7 +39831,7 @@
         <v>46088</v>
       </c>
       <c r="C212" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D212" t="str">
         <v>Broaster</v>
@@ -39854,7 +39854,7 @@
         <v>46088</v>
       </c>
       <c r="C213" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D213" t="str">
         <v>Gaseosa</v>
@@ -39877,7 +39877,7 @@
         <v>46088</v>
       </c>
       <c r="C214" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D214" t="str">
         <v>Polo</v>
@@ -39900,7 +39900,7 @@
         <v>46088</v>
       </c>
       <c r="C215" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D215" t="str">
         <v>Ron</v>
@@ -39923,7 +39923,7 @@
         <v>46088</v>
       </c>
       <c r="C216" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D216" t="str">
         <v>Gaseosa</v>
@@ -39946,7 +39946,7 @@
         <v>46089</v>
       </c>
       <c r="C217" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D217" t="str">
         <v>Salida Familiar</v>
@@ -39969,7 +39969,7 @@
         <v>46090</v>
       </c>
       <c r="C218" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D218" t="str">
         <v>Utencilios de Aseo Personal</v>
@@ -39992,7 +39992,7 @@
         <v>46090</v>
       </c>
       <c r="C219" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D219" t="str">
         <v>Broaster</v>
@@ -40015,7 +40015,7 @@
         <v>46091</v>
       </c>
       <c r="C220" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D220" t="str">
         <v>Taxi</v>
@@ -40038,7 +40038,7 @@
         <v>46091</v>
       </c>
       <c r="C221" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D221" t="str">
         <v>Utencilios de Limpieza</v>
@@ -40061,7 +40061,7 @@
         <v>46091</v>
       </c>
       <c r="C222" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D222" t="str">
         <v>Torta de Chocolate</v>
@@ -40084,7 +40084,7 @@
         <v>46095</v>
       </c>
       <c r="C223" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D223" t="str">
         <v>iCloud</v>
@@ -40107,7 +40107,7 @@
         <v>46096</v>
       </c>
       <c r="C224" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D224" t="str">
         <v>Yape Crédito</v>
@@ -40130,7 +40130,7 @@
         <v>46096</v>
       </c>
       <c r="C225" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D225" t="str">
         <v>Telefonia Movil</v>
@@ -40153,7 +40153,7 @@
         <v>46096</v>
       </c>
       <c r="C226" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D226" t="str">
         <v>Venta de iPhone</v>
@@ -40176,7 +40176,7 @@
         <v>46096</v>
       </c>
       <c r="C227" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D227" t="str">
         <v>Concierto Milo J</v>
@@ -40199,7 +40199,7 @@
         <v>46102</v>
       </c>
       <c r="C228" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D228" t="str">
         <v>Cumpleaños Madre</v>
@@ -40222,7 +40222,7 @@
         <v>46102</v>
       </c>
       <c r="C229" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D229" t="str">
         <v>Broaster</v>
@@ -40245,7 +40245,7 @@
         <v>46105</v>
       </c>
       <c r="C230" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D230" t="str">
         <v>Bus</v>
@@ -40268,7 +40268,7 @@
         <v>46105</v>
       </c>
       <c r="C231" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D231" t="str">
         <v>Hamburguesa</v>
@@ -40291,7 +40291,7 @@
         <v>46107</v>
       </c>
       <c r="C232" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D232" t="str">
         <v>Bus</v>
@@ -40314,7 +40314,7 @@
         <v>46113</v>
       </c>
       <c r="C233" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D233" t="str">
         <v>Bonificación Ahorro</v>
@@ -40337,7 +40337,7 @@
         <v>46113</v>
       </c>
       <c r="C234" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D234" t="str">
         <v>Sueldo</v>
@@ -40360,7 +40360,7 @@
         <v>46113</v>
       </c>
       <c r="C235" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D235" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -40383,7 +40383,7 @@
         <v>46113</v>
       </c>
       <c r="C236" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D236" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -40406,7 +40406,7 @@
         <v>46113</v>
       </c>
       <c r="C237" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D237" t="str">
         <v>iPhone 16</v>
@@ -40429,7 +40429,7 @@
         <v>46113</v>
       </c>
       <c r="C238" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D238" t="str">
         <v>Linea Tarjeta</v>
@@ -40452,7 +40452,7 @@
         <v>46113</v>
       </c>
       <c r="C239" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D239" t="str">
         <v>Viaje Laraos</v>
@@ -40475,7 +40475,7 @@
         <v>46113</v>
       </c>
       <c r="C240" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D240" t="str">
         <v>Viaje Piura</v>
@@ -40498,7 +40498,7 @@
         <v>46113</v>
       </c>
       <c r="C241" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D241" t="str">
         <v>Broaster</v>
@@ -40521,7 +40521,7 @@
         <v>46113</v>
       </c>
       <c r="C242" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D242" t="str">
         <v>Chifa</v>
@@ -40544,7 +40544,7 @@
         <v>46113</v>
       </c>
       <c r="C243" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D243" t="str">
         <v>Comida</v>
@@ -40567,7 +40567,7 @@
         <v>46113</v>
       </c>
       <c r="C244" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D244" t="str">
         <v>Internet</v>
@@ -40590,7 +40590,7 @@
         <v>46113</v>
       </c>
       <c r="C245" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D245" t="str">
         <v>Viaje Raura</v>
@@ -40613,7 +40613,7 @@
         <v>46113</v>
       </c>
       <c r="C246" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D246" t="str">
         <v>Broaster</v>
@@ -40636,7 +40636,7 @@
         <v>46113</v>
       </c>
       <c r="C247" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D247" t="str">
         <v>Psicologo</v>
@@ -40659,7 +40659,7 @@
         <v>46113</v>
       </c>
       <c r="C248" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D248" t="str">
         <v>Luz</v>
@@ -40682,7 +40682,7 @@
         <v>46113</v>
       </c>
       <c r="C249" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D249" t="str">
         <v>Gas</v>
@@ -40705,7 +40705,7 @@
         <v>46113</v>
       </c>
       <c r="C250" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D250" t="str">
         <v>Corte de Cabello</v>
@@ -40728,7 +40728,7 @@
         <v>46113</v>
       </c>
       <c r="C251" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D251" t="str">
         <v>Mayra</v>
@@ -40751,7 +40751,7 @@
         <v>46113</v>
       </c>
       <c r="C252" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D252" t="str">
         <v>Menú</v>
@@ -40774,7 +40774,7 @@
         <v>46113</v>
       </c>
       <c r="C253" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D253" t="str">
         <v>Spotify</v>
@@ -40797,7 +40797,7 @@
         <v>46113</v>
       </c>
       <c r="C254" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D254" t="str">
         <v>Taxi</v>
@@ -40820,7 +40820,7 @@
         <v>46113</v>
       </c>
       <c r="C255" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D255" t="str">
         <v>Agua + Mantenimiento</v>
@@ -40843,7 +40843,7 @@
         <v>46114</v>
       </c>
       <c r="C256" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D256" t="str">
         <v>Pantalon</v>
@@ -40866,7 +40866,7 @@
         <v>46114</v>
       </c>
       <c r="C257" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D257" t="str">
         <v>Cumpleaños Adriano</v>
@@ -40889,7 +40889,7 @@
         <v>46114</v>
       </c>
       <c r="C258" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D258" t="str">
         <v>Broaster</v>
@@ -40912,7 +40912,7 @@
         <v>46115</v>
       </c>
       <c r="C259" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D259" t="str">
         <v>Viaje Piura</v>
@@ -40935,7 +40935,7 @@
         <v>46115</v>
       </c>
       <c r="C260" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D260" t="str">
         <v>Viaje Piura</v>
@@ -40958,7 +40958,7 @@
         <v>46116</v>
       </c>
       <c r="C261" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D261" t="str">
         <v>Viaje Piura</v>
@@ -40981,7 +40981,7 @@
         <v>46116</v>
       </c>
       <c r="C262" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D262" t="str">
         <v>Viaje Piura</v>
@@ -41004,7 +41004,7 @@
         <v>46117</v>
       </c>
       <c r="C263" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D263" t="str">
         <v>Viaje Piura</v>
@@ -41027,7 +41027,7 @@
         <v>46118</v>
       </c>
       <c r="C264" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D264" t="str">
         <v>Viaje Piura</v>
@@ -41050,7 +41050,7 @@
         <v>46118</v>
       </c>
       <c r="C265" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D265" t="str">
         <v>Madre</v>
@@ -41073,7 +41073,7 @@
         <v>46119</v>
       </c>
       <c r="C266" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D266" t="str">
         <v>Viaje Piura</v>
@@ -41096,7 +41096,7 @@
         <v>46120</v>
       </c>
       <c r="C267" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D267" t="str">
         <v>Utencilios de Limpieza</v>
@@ -41119,7 +41119,7 @@
         <v>46121</v>
       </c>
       <c r="C268" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D268" t="str">
         <v>Gaseosa</v>
@@ -41142,7 +41142,7 @@
         <v>46121</v>
       </c>
       <c r="C269" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D269" t="str">
         <v>Hotel</v>
@@ -41165,7 +41165,7 @@
         <v>46121</v>
       </c>
       <c r="C270" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D270" t="str">
         <v>Cumpleaños Alondra</v>
@@ -41188,7 +41188,7 @@
         <v>46121</v>
       </c>
       <c r="C271" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D271" t="str">
         <v>Broaster</v>
@@ -41211,7 +41211,7 @@
         <v>46121</v>
       </c>
       <c r="C272" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D272" t="str">
         <v>Milagros</v>
@@ -41234,7 +41234,7 @@
         <v>46122</v>
       </c>
       <c r="C273" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D273" t="str">
         <v>Broaster</v>
@@ -41257,7 +41257,7 @@
         <v>46122</v>
       </c>
       <c r="C274" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D274" t="str">
         <v>Taxi</v>
@@ -41280,7 +41280,7 @@
         <v>46122</v>
       </c>
       <c r="C275" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D275" t="str">
         <v>Taxi</v>
@@ -41303,7 +41303,7 @@
         <v>46123</v>
       </c>
       <c r="C276" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D276" t="str">
         <v>Hotel</v>
@@ -41326,7 +41326,7 @@
         <v>46126</v>
       </c>
       <c r="C277" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D277" t="str">
         <v>iCloud</v>
@@ -41349,7 +41349,7 @@
         <v>46127</v>
       </c>
       <c r="C278" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D278" t="str">
         <v>Telefonia Movil</v>
@@ -41372,7 +41372,7 @@
         <v>46127</v>
       </c>
       <c r="C279" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D279" t="str">
         <v>Yape Crédito</v>
@@ -41395,7 +41395,7 @@
         <v>46127</v>
       </c>
       <c r="C280" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D280" t="str">
         <v>Madre</v>
@@ -41418,7 +41418,7 @@
         <v>46128</v>
       </c>
       <c r="C281" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D281" t="str">
         <v>Madre</v>
@@ -41441,7 +41441,7 @@
         <v>46129</v>
       </c>
       <c r="C282" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D282" t="str">
         <v>Padre</v>
@@ -41464,7 +41464,7 @@
         <v>46129</v>
       </c>
       <c r="C283" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D283" t="str">
         <v>Futbol</v>
@@ -41487,7 +41487,7 @@
         <v>46129</v>
       </c>
       <c r="C284" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D284" t="str">
         <v>Concierto Milo J</v>
@@ -41510,7 +41510,7 @@
         <v>46130</v>
       </c>
       <c r="C285" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D285" t="str">
         <v>Cumpleaños Beu</v>
@@ -41533,7 +41533,7 @@
         <v>46130</v>
       </c>
       <c r="C286" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D286" t="str">
         <v>Hotel</v>
@@ -41556,7 +41556,7 @@
         <v>46130</v>
       </c>
       <c r="C287" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D287" t="str">
         <v>Hamburguesa</v>
@@ -41579,7 +41579,7 @@
         <v>46131</v>
       </c>
       <c r="C288" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D288" t="str">
         <v>Gaseosa</v>
@@ -41602,7 +41602,7 @@
         <v>46132</v>
       </c>
       <c r="C289" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D289" t="str">
         <v>Broaster</v>
@@ -41625,7 +41625,7 @@
         <v>46136</v>
       </c>
       <c r="C290" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D290" t="str">
         <v>Cine</v>
@@ -41648,7 +41648,7 @@
         <v>46137</v>
       </c>
       <c r="C291" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D291" t="str">
         <v>Desvagramen</v>
@@ -41671,7 +41671,7 @@
         <v>46137</v>
       </c>
       <c r="C292" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D292" t="str">
         <v>Taxi</v>
@@ -41694,7 +41694,7 @@
         <v>46138</v>
       </c>
       <c r="C293" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D293" t="str">
         <v>Futbol</v>
@@ -41717,7 +41717,7 @@
         <v>46143</v>
       </c>
       <c r="C294" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D294" t="str">
         <v>Bonificación Ahorro</v>
@@ -41740,7 +41740,7 @@
         <v>46143</v>
       </c>
       <c r="C295" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D295" t="str">
         <v>Sueldo</v>
@@ -41763,7 +41763,7 @@
         <v>46143</v>
       </c>
       <c r="C296" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D296" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -41786,7 +41786,7 @@
         <v>46143</v>
       </c>
       <c r="C297" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D297" t="str">
         <v>Yape Crédito</v>
@@ -41809,7 +41809,7 @@
         <v>46143</v>
       </c>
       <c r="C298" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D298" t="str">
         <v>Aaron</v>
@@ -41832,7 +41832,7 @@
         <v>46143</v>
       </c>
       <c r="C299" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D299" t="str">
         <v>iPhone 16</v>
@@ -41855,7 +41855,7 @@
         <v>46143</v>
       </c>
       <c r="C300" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D300" t="str">
         <v>Aaron</v>
@@ -41878,7 +41878,7 @@
         <v>46143</v>
       </c>
       <c r="C301" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D301" t="str">
         <v>Linea Tarjeta</v>
@@ -41901,7 +41901,7 @@
         <v>46143</v>
       </c>
       <c r="C302" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D302" t="str">
         <v>Jacko</v>
@@ -41924,7 +41924,7 @@
         <v>46143</v>
       </c>
       <c r="C303" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D303" t="str">
         <v>Broaster</v>
@@ -41947,7 +41947,7 @@
         <v>46143</v>
       </c>
       <c r="C304" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D304" t="str">
         <v>Dia del Trabajador</v>
@@ -41970,7 +41970,7 @@
         <v>46143</v>
       </c>
       <c r="C305" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D305" t="str">
         <v>Utencilios de Limpieza</v>
@@ -41993,7 +41993,7 @@
         <v>46143</v>
       </c>
       <c r="C306" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D306" t="str">
         <v>Internet</v>
@@ -42016,7 +42016,7 @@
         <v>46143</v>
       </c>
       <c r="C307" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D307" t="str">
         <v>Luz</v>
@@ -42039,7 +42039,7 @@
         <v>46143</v>
       </c>
       <c r="C308" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D308" t="str">
         <v>Gas</v>
@@ -42062,7 +42062,7 @@
         <v>46143</v>
       </c>
       <c r="C309" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D309" t="str">
         <v>Corte de Cabello</v>
@@ -42085,7 +42085,7 @@
         <v>46143</v>
       </c>
       <c r="C310" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D310" t="str">
         <v>Padre</v>
@@ -42108,7 +42108,7 @@
         <v>46143</v>
       </c>
       <c r="C311" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D311" t="str">
         <v>Taxi</v>
@@ -42131,7 +42131,7 @@
         <v>46143</v>
       </c>
       <c r="C312" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D312" t="str">
         <v>Café</v>
@@ -42154,7 +42154,7 @@
         <v>46143</v>
       </c>
       <c r="C313" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D313" t="str">
         <v>Broaster</v>
@@ -42177,7 +42177,7 @@
         <v>46143</v>
       </c>
       <c r="C314" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D314" t="str">
         <v>Dia del Trabajador</v>
@@ -42200,7 +42200,7 @@
         <v>46143</v>
       </c>
       <c r="C315" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D315" t="str">
         <v>Spotify</v>
@@ -42223,7 +42223,7 @@
         <v>46143</v>
       </c>
       <c r="C316" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D316" t="str">
         <v>Agua + Mantenimiento</v>
@@ -42246,7 +42246,7 @@
         <v>46144</v>
       </c>
       <c r="C317" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D317" t="str">
         <v>Broaster</v>
@@ -42269,7 +42269,7 @@
         <v>46144</v>
       </c>
       <c r="C318" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D318" t="str">
         <v>Gaseosa</v>
@@ -42292,7 +42292,7 @@
         <v>46145</v>
       </c>
       <c r="C319" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D319" t="str">
         <v>Pollo a la Brasa</v>
@@ -42315,7 +42315,7 @@
         <v>46146</v>
       </c>
       <c r="C320" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D320" t="str">
         <v>IA</v>
@@ -42338,7 +42338,7 @@
         <v>46146</v>
       </c>
       <c r="C321" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D321" t="str">
         <v>Dia de la Madre</v>
@@ -42361,7 +42361,7 @@
         <v>46146</v>
       </c>
       <c r="C322" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D322" t="str">
         <v>Broaster</v>
@@ -42384,7 +42384,7 @@
         <v>46147</v>
       </c>
       <c r="C323" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D323" t="str">
         <v>Gaseosa</v>
@@ -42407,7 +42407,7 @@
         <v>46147</v>
       </c>
       <c r="C324" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D324" t="str">
         <v>Broaster</v>
@@ -42430,7 +42430,7 @@
         <v>46148</v>
       </c>
       <c r="C325" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D325" t="str">
         <v>Utencilios de Limpieza</v>
@@ -42453,7 +42453,7 @@
         <v>46148</v>
       </c>
       <c r="C326" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D326" t="str">
         <v>Taxi</v>
@@ -42476,7 +42476,7 @@
         <v>46149</v>
       </c>
       <c r="C327" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D327" t="str">
         <v>Broaster</v>
@@ -42499,7 +42499,7 @@
         <v>46149</v>
       </c>
       <c r="C328" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D328" t="str">
         <v>Condones</v>
@@ -42522,7 +42522,7 @@
         <v>46150</v>
       </c>
       <c r="C329" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D329" t="str">
         <v>Broaster</v>
@@ -42545,7 +42545,7 @@
         <v>46151</v>
       </c>
       <c r="C330" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D330" t="str">
         <v>Taxi</v>
@@ -42568,7 +42568,7 @@
         <v>46151</v>
       </c>
       <c r="C331" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D331" t="str">
         <v>Dia de la Madre</v>
@@ -42591,7 +42591,7 @@
         <v>46152</v>
       </c>
       <c r="C332" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D332" t="str">
         <v>Dia de la Madre</v>
@@ -42614,7 +42614,7 @@
         <v>46154</v>
       </c>
       <c r="C333" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D333" t="str">
         <v>Entrada Estadio</v>
@@ -42637,7 +42637,7 @@
         <v>46154</v>
       </c>
       <c r="C334" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D334" t="str">
         <v>Dulce</v>
@@ -42660,7 +42660,7 @@
         <v>46154</v>
       </c>
       <c r="C335" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D335" t="str">
         <v>Bus</v>
@@ -42683,7 +42683,7 @@
         <v>46154</v>
       </c>
       <c r="C336" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D336" t="str">
         <v>Futbol</v>
@@ -42706,7 +42706,7 @@
         <v>46154</v>
       </c>
       <c r="C337" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D337" t="str">
         <v>Broaster</v>
@@ -42729,7 +42729,7 @@
         <v>46154</v>
       </c>
       <c r="C338" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D338" t="str">
         <v>Dulce</v>
@@ -42752,7 +42752,7 @@
         <v>46155</v>
       </c>
       <c r="C339" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D339" t="str">
         <v>CTS</v>
@@ -42775,7 +42775,7 @@
         <v>46155</v>
       </c>
       <c r="C340" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D340" t="str">
         <v>Titulación</v>
@@ -42798,7 +42798,7 @@
         <v>46156</v>
       </c>
       <c r="C341" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D341" t="str">
         <v>Polo</v>
@@ -42821,7 +42821,7 @@
         <v>46156</v>
       </c>
       <c r="C342" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D342" t="str">
         <v>Broaster</v>
@@ -42844,7 +42844,7 @@
         <v>46156</v>
       </c>
       <c r="C343" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D343" t="str">
         <v>iCloud</v>
@@ -42867,7 +42867,7 @@
         <v>46157</v>
       </c>
       <c r="C344" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D344" t="str">
         <v>Telefonia Movil</v>
@@ -42890,7 +42890,7 @@
         <v>46157</v>
       </c>
       <c r="C345" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D345" t="str">
         <v>Comida</v>
@@ -42913,7 +42913,7 @@
         <v>46158</v>
       </c>
       <c r="C346" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D346" t="str">
         <v>Gaseosa</v>
@@ -42936,7 +42936,7 @@
         <v>46158</v>
       </c>
       <c r="C347" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D347" t="str">
         <v>Camisa</v>
@@ -42959,7 +42959,7 @@
         <v>46158</v>
       </c>
       <c r="C348" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D348" t="str">
         <v>Pantalon</v>
@@ -42982,7 +42982,7 @@
         <v>46158</v>
       </c>
       <c r="C349" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D349" t="str">
         <v>Futbol</v>
@@ -43005,7 +43005,7 @@
         <v>46158</v>
       </c>
       <c r="C350" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D350" t="str">
         <v>Futbol</v>
@@ -43028,7 +43028,7 @@
         <v>46160</v>
       </c>
       <c r="C351" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D351" t="str">
         <v>Madre</v>
@@ -43051,7 +43051,7 @@
         <v>46160</v>
       </c>
       <c r="C352" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D352" t="str">
         <v>Taxi</v>
@@ -43074,7 +43074,7 @@
         <v>46160</v>
       </c>
       <c r="C353" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D353" t="str">
         <v>Broaster</v>
@@ -43097,7 +43097,7 @@
         <v>46160</v>
       </c>
       <c r="C354" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D354" t="str">
         <v>Bus</v>
@@ -43120,7 +43120,7 @@
         <v>46161</v>
       </c>
       <c r="C355" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D355" t="str">
         <v>Corte de Cabello</v>
@@ -43143,7 +43143,7 @@
         <v>46163</v>
       </c>
       <c r="C356" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D356" t="str">
         <v>Futbol</v>
@@ -43166,7 +43166,7 @@
         <v>46164</v>
       </c>
       <c r="C357" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D357" t="str">
         <v>Concierto  Soda Stereo</v>
@@ -43189,7 +43189,7 @@
         <v>46165</v>
       </c>
       <c r="C358" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D358" t="str">
         <v>Broaster</v>
@@ -43212,7 +43212,7 @@
         <v>46168</v>
       </c>
       <c r="C359" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D359" t="str">
         <v>Café</v>
@@ -43235,7 +43235,7 @@
         <v>46168</v>
       </c>
       <c r="C360" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D360" t="str">
         <v>Apuestas</v>
@@ -43258,7 +43258,7 @@
         <v>46169</v>
       </c>
       <c r="C361" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D361" t="str">
         <v>Café</v>
@@ -43281,7 +43281,7 @@
         <v>46174</v>
       </c>
       <c r="C362" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D362" t="str">
         <v>Bonificación Ahorro</v>
@@ -43304,7 +43304,7 @@
         <v>46174</v>
       </c>
       <c r="C363" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D363" t="str">
         <v>Sueldo</v>
@@ -43327,7 +43327,7 @@
         <v>46174</v>
       </c>
       <c r="C364" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D364" t="str">
         <v>Linea Tarjeta</v>
@@ -43350,7 +43350,7 @@
         <v>46174</v>
       </c>
       <c r="C365" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D365" t="str">
         <v>Linea Tarjeta</v>
@@ -43373,7 +43373,7 @@
         <v>46174</v>
       </c>
       <c r="C366" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D366" t="str">
         <v>Padre</v>
@@ -43396,7 +43396,7 @@
         <v>46174</v>
       </c>
       <c r="C367" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D367" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -43419,7 +43419,7 @@
         <v>46174</v>
       </c>
       <c r="C368" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D368" t="str">
         <v>Corte de Cabello</v>
@@ -43442,7 +43442,7 @@
         <v>46174</v>
       </c>
       <c r="C369" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D369" t="str">
         <v>Titulación</v>
@@ -43465,7 +43465,7 @@
         <v>46174</v>
       </c>
       <c r="C370" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D370" t="str">
         <v>Madre</v>
@@ -43488,7 +43488,7 @@
         <v>46174</v>
       </c>
       <c r="C371" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D371" t="str">
         <v>Carol</v>
@@ -43511,7 +43511,7 @@
         <v>46174</v>
       </c>
       <c r="C372" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D372" t="str">
         <v>Utencilios de Limpieza</v>
@@ -43534,7 +43534,7 @@
         <v>46174</v>
       </c>
       <c r="C373" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D373" t="str">
         <v>Café</v>
@@ -43557,7 +43557,7 @@
         <v>46174</v>
       </c>
       <c r="C374" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D374" t="str">
         <v>iPhone 16</v>
@@ -43580,7 +43580,7 @@
         <v>46174</v>
       </c>
       <c r="C375" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D375" t="str">
         <v>HappyLand</v>
@@ -43603,7 +43603,7 @@
         <v>46174</v>
       </c>
       <c r="C376" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D376" t="str">
         <v>Makis</v>
@@ -43626,7 +43626,7 @@
         <v>46174</v>
       </c>
       <c r="C377" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D377" t="str">
         <v>Bus</v>
@@ -43649,7 +43649,7 @@
         <v>46174</v>
       </c>
       <c r="C378" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D378" t="str">
         <v>Broaster</v>
@@ -43672,7 +43672,7 @@
         <v>46174</v>
       </c>
       <c r="C379" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D379" t="str">
         <v>Gaseosa</v>
@@ -43695,7 +43695,7 @@
         <v>46174</v>
       </c>
       <c r="C380" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D380" t="str">
         <v>Tatuaje</v>
@@ -43718,7 +43718,7 @@
         <v>46174</v>
       </c>
       <c r="C381" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D381" t="str">
         <v>Bowling</v>
@@ -43741,7 +43741,7 @@
         <v>46174</v>
       </c>
       <c r="C382" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D382" t="str">
         <v>Bus</v>
@@ -43764,7 +43764,7 @@
         <v>46174</v>
       </c>
       <c r="C383" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D383" t="str">
         <v>Bus</v>
@@ -43787,7 +43787,7 @@
         <v>46174</v>
       </c>
       <c r="C384" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D384" t="str">
         <v>Bepanten</v>
@@ -43810,7 +43810,7 @@
         <v>46174</v>
       </c>
       <c r="C385" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D385" t="str">
         <v>Futbol</v>
@@ -43833,7 +43833,7 @@
         <v>46174</v>
       </c>
       <c r="C386" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D386" t="str">
         <v>Chicharron</v>
@@ -43856,7 +43856,7 @@
         <v>46174</v>
       </c>
       <c r="C387" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D387" t="str">
         <v>Padre</v>
@@ -43879,7 +43879,7 @@
         <v>46174</v>
       </c>
       <c r="C388" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D388" t="str">
         <v>Spotify</v>
@@ -43902,7 +43902,7 @@
         <v>46174</v>
       </c>
       <c r="C389" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D389" t="str">
         <v>Milagros</v>
@@ -43925,7 +43925,7 @@
         <v>46174</v>
       </c>
       <c r="C390" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D390" t="str">
         <v>Agua + Mantenimiento</v>
@@ -43948,7 +43948,7 @@
         <v>46174</v>
       </c>
       <c r="C391" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D391" t="str">
         <v>Internet</v>
@@ -43971,7 +43971,7 @@
         <v>46174</v>
       </c>
       <c r="C392" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D392" t="str">
         <v>Luz</v>
@@ -43994,7 +43994,7 @@
         <v>46174</v>
       </c>
       <c r="C393" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D393" t="str">
         <v>Gas</v>
@@ -44017,7 +44017,7 @@
         <v>46175</v>
       </c>
       <c r="C394" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D394" t="str">
         <v>Cine</v>
@@ -44040,7 +44040,7 @@
         <v>46175</v>
       </c>
       <c r="C395" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D395" t="str">
         <v>Bus</v>
@@ -44063,7 +44063,7 @@
         <v>46175</v>
       </c>
       <c r="C396" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D396" t="str">
         <v>Carol</v>
@@ -44086,7 +44086,7 @@
         <v>46175</v>
       </c>
       <c r="C397" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D397" t="str">
         <v>Bus</v>
@@ -44109,7 +44109,7 @@
         <v>46176</v>
       </c>
       <c r="C398" t="str">
-        <v>Regalos &amp; Celebraciones</v>
+        <v>Gasto</v>
       </c>
       <c r="D398" t="str">
         <v>Cumpleaños Padre</v>
@@ -44132,7 +44132,7 @@
         <v>46178</v>
       </c>
       <c r="C399" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D399" t="str">
         <v>Cine</v>
@@ -44155,7 +44155,7 @@
         <v>46178</v>
       </c>
       <c r="C400" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D400" t="str">
         <v>Café</v>
@@ -44178,7 +44178,7 @@
         <v>46178</v>
       </c>
       <c r="C401" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D401" t="str">
         <v>Taxi</v>
@@ -44201,7 +44201,7 @@
         <v>46178</v>
       </c>
       <c r="C402" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D402" t="str">
         <v>Fridays</v>
@@ -44224,7 +44224,7 @@
         <v>46178</v>
       </c>
       <c r="C403" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D403" t="str">
         <v>Karts</v>
@@ -44247,7 +44247,7 @@
         <v>46178</v>
       </c>
       <c r="C404" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D404" t="str">
         <v>Desvagramen</v>
@@ -44270,7 +44270,7 @@
         <v>46178</v>
       </c>
       <c r="C405" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Gasto</v>
       </c>
       <c r="D405" t="str">
         <v>Fifa 26</v>
@@ -44293,7 +44293,7 @@
         <v>46180</v>
       </c>
       <c r="C406" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D406" t="str">
         <v>Chifa</v>
@@ -44316,7 +44316,7 @@
         <v>46181</v>
       </c>
       <c r="C407" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D407" t="str">
         <v>Apuestas</v>
@@ -44339,7 +44339,7 @@
         <v>46181</v>
       </c>
       <c r="C408" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D408" t="str">
         <v>Prestamo BCP</v>
@@ -44362,7 +44362,7 @@
         <v>46181</v>
       </c>
       <c r="C409" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D409" t="str">
         <v>Viaje Brasil</v>
@@ -44385,7 +44385,7 @@
         <v>46181</v>
       </c>
       <c r="C410" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D410" t="str">
         <v>Futbol</v>
@@ -44408,7 +44408,7 @@
         <v>46181</v>
       </c>
       <c r="C411" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D411" t="str">
         <v>Taxi</v>
@@ -44431,7 +44431,7 @@
         <v>46182</v>
       </c>
       <c r="C412" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D412" t="str">
         <v>Café</v>
@@ -44454,7 +44454,7 @@
         <v>46182</v>
       </c>
       <c r="C413" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D413" t="str">
         <v>Bus</v>
@@ -44477,7 +44477,7 @@
         <v>46182</v>
       </c>
       <c r="C414" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D414" t="str">
         <v>Café</v>
@@ -44500,7 +44500,7 @@
         <v>46182</v>
       </c>
       <c r="C415" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D415" t="str">
         <v>Bus</v>
@@ -44523,7 +44523,7 @@
         <v>46182</v>
       </c>
       <c r="C416" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D416" t="str">
         <v>Bus</v>
@@ -44546,7 +44546,7 @@
         <v>46182</v>
       </c>
       <c r="C417" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D417" t="str">
         <v>Café</v>
@@ -44569,7 +44569,7 @@
         <v>46182</v>
       </c>
       <c r="C418" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D418" t="str">
         <v>Planet Chicken</v>
@@ -44592,7 +44592,7 @@
         <v>46183</v>
       </c>
       <c r="C419" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D419" t="str">
         <v>Café</v>
@@ -44615,7 +44615,7 @@
         <v>46183</v>
       </c>
       <c r="C420" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D420" t="str">
         <v>Chifa</v>
@@ -44638,7 +44638,7 @@
         <v>46183</v>
       </c>
       <c r="C421" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D421" t="str">
         <v>Bus</v>
@@ -44661,7 +44661,7 @@
         <v>46183</v>
       </c>
       <c r="C422" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D422" t="str">
         <v>Taxi</v>
@@ -44684,7 +44684,7 @@
         <v>46184</v>
       </c>
       <c r="C423" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D423" t="str">
         <v>Streaming</v>
@@ -44707,7 +44707,7 @@
         <v>46184</v>
       </c>
       <c r="C424" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D424" t="str">
         <v>Hotel</v>
@@ -44730,7 +44730,7 @@
         <v>46184</v>
       </c>
       <c r="C425" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D425" t="str">
         <v>Condones</v>
@@ -44753,7 +44753,7 @@
         <v>46184</v>
       </c>
       <c r="C426" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D426" t="str">
         <v>Agua Mineral</v>
@@ -44776,7 +44776,7 @@
         <v>46184</v>
       </c>
       <c r="C427" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D427" t="str">
         <v>Prestamo Yape</v>
@@ -44799,7 +44799,7 @@
         <v>46184</v>
       </c>
       <c r="C428" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D428" t="str">
         <v>Gaseosa</v>
@@ -44822,7 +44822,7 @@
         <v>46184</v>
       </c>
       <c r="C429" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D429" t="str">
         <v>Figuritas</v>
@@ -44845,7 +44845,7 @@
         <v>46185</v>
       </c>
       <c r="C430" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D430" t="str">
         <v>Broaster</v>
@@ -44868,7 +44868,7 @@
         <v>46185</v>
       </c>
       <c r="C431" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D431" t="str">
         <v>Bus</v>
@@ -44891,7 +44891,7 @@
         <v>46186</v>
       </c>
       <c r="C432" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D432" t="str">
         <v>Carol</v>
@@ -44914,7 +44914,7 @@
         <v>46186</v>
       </c>
       <c r="C433" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D433" t="str">
         <v>Broaster</v>
@@ -44937,7 +44937,7 @@
         <v>46186</v>
       </c>
       <c r="C434" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D434" t="str">
         <v>Taxi</v>
@@ -44960,7 +44960,7 @@
         <v>46186</v>
       </c>
       <c r="C435" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D435" t="str">
         <v>Café</v>
@@ -44983,7 +44983,7 @@
         <v>46186</v>
       </c>
       <c r="C436" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D436" t="str">
         <v>Taxi</v>
@@ -45006,7 +45006,7 @@
         <v>46186</v>
       </c>
       <c r="C437" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D437" t="str">
         <v>Casaca</v>
@@ -45029,7 +45029,7 @@
         <v>46186</v>
       </c>
       <c r="C438" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D438" t="str">
         <v>Dollarcity</v>
@@ -45052,7 +45052,7 @@
         <v>46186</v>
       </c>
       <c r="C439" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D439" t="str">
         <v>Café</v>
@@ -45075,7 +45075,7 @@
         <v>46186</v>
       </c>
       <c r="C440" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D440" t="str">
         <v>Bus</v>
@@ -45098,7 +45098,7 @@
         <v>46186</v>
       </c>
       <c r="C441" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D441" t="str">
         <v>Carol</v>
@@ -45121,7 +45121,7 @@
         <v>46186</v>
       </c>
       <c r="C442" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D442" t="str">
         <v>Gaseosa</v>
@@ -45144,7 +45144,7 @@
         <v>46186</v>
       </c>
       <c r="C443" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D443" t="str">
         <v>Dollarcity</v>
@@ -45167,7 +45167,7 @@
         <v>46186</v>
       </c>
       <c r="C444" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D444" t="str">
         <v>Bus</v>
@@ -45190,7 +45190,7 @@
         <v>46186</v>
       </c>
       <c r="C445" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D445" t="str">
         <v>Abrigo</v>
@@ -45213,7 +45213,7 @@
         <v>46186</v>
       </c>
       <c r="C446" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D446" t="str">
         <v>Carol</v>
@@ -45236,7 +45236,7 @@
         <v>46187</v>
       </c>
       <c r="C447" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D447" t="str">
         <v>iCloud</v>
@@ -45259,7 +45259,7 @@
         <v>46187</v>
       </c>
       <c r="C448" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D448" t="str">
         <v>Broaster</v>
@@ -45282,7 +45282,7 @@
         <v>46188</v>
       </c>
       <c r="C449" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D449" t="str">
         <v>Telefonia Movil</v>
@@ -45305,7 +45305,7 @@
         <v>46188</v>
       </c>
       <c r="C450" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D450" t="str">
         <v>IA</v>
@@ -45328,7 +45328,7 @@
         <v>46188</v>
       </c>
       <c r="C451" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D451" t="str">
         <v>IA</v>
@@ -45351,7 +45351,7 @@
         <v>46189</v>
       </c>
       <c r="C452" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D452" t="str">
         <v>Bus</v>
@@ -45374,7 +45374,7 @@
         <v>46189</v>
       </c>
       <c r="C453" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D453" t="str">
         <v>Café</v>
@@ -45397,7 +45397,7 @@
         <v>46189</v>
       </c>
       <c r="C454" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D454" t="str">
         <v>Broaster</v>
@@ -45420,7 +45420,7 @@
         <v>46190</v>
       </c>
       <c r="C455" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D455" t="str">
         <v>Broaster</v>
@@ -45443,7 +45443,7 @@
         <v>46192</v>
       </c>
       <c r="C456" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D456" t="str">
         <v>Apuestas</v>
@@ -45466,7 +45466,7 @@
         <v>46192</v>
       </c>
       <c r="C457" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D457" t="str">
         <v>Gaseosa</v>
@@ -45489,7 +45489,7 @@
         <v>46192</v>
       </c>
       <c r="C458" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D458" t="str">
         <v>Futbol</v>
@@ -45512,7 +45512,7 @@
         <v>46193</v>
       </c>
       <c r="C459" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D459" t="str">
         <v>Bus</v>
@@ -45535,7 +45535,7 @@
         <v>46193</v>
       </c>
       <c r="C460" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D460" t="str">
         <v>Bus</v>
@@ -45558,7 +45558,7 @@
         <v>46193</v>
       </c>
       <c r="C461" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D461" t="str">
         <v>Figuritas</v>
@@ -45581,7 +45581,7 @@
         <v>46193</v>
       </c>
       <c r="C462" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D462" t="str">
         <v>Menú</v>
@@ -45604,7 +45604,7 @@
         <v>46193</v>
       </c>
       <c r="C463" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D463" t="str">
         <v>Dulce de Leche</v>
@@ -45627,7 +45627,7 @@
         <v>46193</v>
       </c>
       <c r="C464" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D464" t="str">
         <v>Futbol</v>
@@ -45650,7 +45650,7 @@
         <v>46194</v>
       </c>
       <c r="C465" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D465" t="str">
         <v>Pollo a la Brasa</v>
@@ -45673,7 +45673,7 @@
         <v>46194</v>
       </c>
       <c r="C466" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D466" t="str">
         <v>Medicina Madre</v>
@@ -45696,7 +45696,7 @@
         <v>46194</v>
       </c>
       <c r="C467" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D467" t="str">
         <v>Medicina Madre</v>
@@ -45719,7 +45719,7 @@
         <v>46195</v>
       </c>
       <c r="C468" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D468" t="str">
         <v>Hotel</v>
@@ -45742,7 +45742,7 @@
         <v>46195</v>
       </c>
       <c r="C469" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D469" t="str">
         <v>Condones</v>
@@ -45765,7 +45765,7 @@
         <v>46195</v>
       </c>
       <c r="C470" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D470" t="str">
         <v>Agua Mineral</v>
@@ -45788,7 +45788,7 @@
         <v>46195</v>
       </c>
       <c r="C471" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D471" t="str">
         <v>Taxi</v>
@@ -45811,7 +45811,7 @@
         <v>46195</v>
       </c>
       <c r="C472" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D472" t="str">
         <v>Utencilios de Limpieza</v>
@@ -45834,7 +45834,7 @@
         <v>46196</v>
       </c>
       <c r="C473" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D473" t="str">
         <v>Medicinas</v>
@@ -45857,7 +45857,7 @@
         <v>46196</v>
       </c>
       <c r="C474" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D474" t="str">
         <v>Broaster</v>
@@ -45880,7 +45880,7 @@
         <v>46204</v>
       </c>
       <c r="C475" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D475" t="str">
         <v>Bonificación Ahorro</v>
@@ -45903,7 +45903,7 @@
         <v>46204</v>
       </c>
       <c r="C476" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D476" t="str">
         <v>Sueldo</v>
@@ -45926,7 +45926,7 @@
         <v>46204</v>
       </c>
       <c r="C477" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D477" t="str">
         <v>Linea Tarjeta</v>
@@ -45949,7 +45949,7 @@
         <v>46204</v>
       </c>
       <c r="C478" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D478" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -45972,7 +45972,7 @@
         <v>46204</v>
       </c>
       <c r="C479" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D479" t="str">
         <v>Linea Tarjeta</v>
@@ -45995,7 +45995,7 @@
         <v>46204</v>
       </c>
       <c r="C480" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D480" t="str">
         <v>Titulación</v>
@@ -46018,7 +46018,7 @@
         <v>46204</v>
       </c>
       <c r="C481" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D481" t="str">
         <v>Internet</v>
@@ -46041,7 +46041,7 @@
         <v>46204</v>
       </c>
       <c r="C482" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D482" t="str">
         <v>Luz</v>
@@ -46064,7 +46064,7 @@
         <v>46204</v>
       </c>
       <c r="C483" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D483" t="str">
         <v>Gas</v>
@@ -46087,7 +46087,7 @@
         <v>46204</v>
       </c>
       <c r="C484" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D484" t="str">
         <v>Prestamo Yape</v>
@@ -46110,7 +46110,7 @@
         <v>46204</v>
       </c>
       <c r="C485" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D485" t="str">
         <v>Agua + Mantenimiento</v>
@@ -46133,7 +46133,7 @@
         <v>46204</v>
       </c>
       <c r="C486" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D486" t="str">
         <v>iPhone 16</v>
@@ -46156,7 +46156,7 @@
         <v>46204</v>
       </c>
       <c r="C487" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D487" t="str">
         <v>Broaster</v>
@@ -46179,7 +46179,7 @@
         <v>46204</v>
       </c>
       <c r="C488" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D488" t="str">
         <v>Bus</v>
@@ -46202,7 +46202,7 @@
         <v>46204</v>
       </c>
       <c r="C489" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D489" t="str">
         <v>Cine</v>
@@ -46225,7 +46225,7 @@
         <v>46204</v>
       </c>
       <c r="C490" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D490" t="str">
         <v>Pollo a la Brasa</v>
@@ -46248,7 +46248,7 @@
         <v>46204</v>
       </c>
       <c r="C491" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D491" t="str">
         <v>Coptel</v>
@@ -46271,7 +46271,7 @@
         <v>46204</v>
       </c>
       <c r="C492" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D492" t="str">
         <v>Bus</v>
@@ -46294,7 +46294,7 @@
         <v>46204</v>
       </c>
       <c r="C493" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D493" t="str">
         <v>Broaster</v>
@@ -46317,7 +46317,7 @@
         <v>46204</v>
       </c>
       <c r="C494" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D494" t="str">
         <v>Utencilios de Limpieza</v>
@@ -46340,7 +46340,7 @@
         <v>46204</v>
       </c>
       <c r="C495" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D495" t="str">
         <v>Broaster</v>
@@ -46363,7 +46363,7 @@
         <v>46204</v>
       </c>
       <c r="C496" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D496" t="str">
         <v>Bus</v>
@@ -46386,7 +46386,7 @@
         <v>46204</v>
       </c>
       <c r="C497" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D497" t="str">
         <v>Café</v>
@@ -46409,7 +46409,7 @@
         <v>46204</v>
       </c>
       <c r="C498" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D498" t="str">
         <v>Carol</v>
@@ -46432,7 +46432,7 @@
         <v>46204</v>
       </c>
       <c r="C499" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D499" t="str">
         <v>Carol</v>
@@ -46455,7 +46455,7 @@
         <v>46204</v>
       </c>
       <c r="C500" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D500" t="str">
         <v>Spotify</v>
@@ -46478,7 +46478,7 @@
         <v>46204</v>
       </c>
       <c r="C501" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D501" t="str">
         <v>Bus</v>
@@ -46501,7 +46501,7 @@
         <v>46204</v>
       </c>
       <c r="C502" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D502" t="str">
         <v>Carol</v>
@@ -46524,7 +46524,7 @@
         <v>46205</v>
       </c>
       <c r="C503" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D503" t="str">
         <v>Linea Tarjeta</v>
@@ -46547,7 +46547,7 @@
         <v>46205</v>
       </c>
       <c r="C504" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D504" t="str">
         <v>Apuestas</v>
@@ -46570,7 +46570,7 @@
         <v>46206</v>
       </c>
       <c r="C505" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D505" t="str">
         <v>Seguro Rimac</v>
@@ -46593,7 +46593,7 @@
         <v>46207</v>
       </c>
       <c r="C506" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D506" t="str">
         <v>Taxi</v>
@@ -46616,7 +46616,7 @@
         <v>46207</v>
       </c>
       <c r="C507" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D507" t="str">
         <v>Desvagramen</v>
@@ -46639,7 +46639,7 @@
         <v>46207</v>
       </c>
       <c r="C508" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D508" t="str">
         <v>Carol</v>
@@ -46662,7 +46662,7 @@
         <v>46207</v>
       </c>
       <c r="C509" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D509" t="str">
         <v>Carol</v>
@@ -46685,7 +46685,7 @@
         <v>46207</v>
       </c>
       <c r="C510" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D510" t="str">
         <v>Carol</v>
@@ -46708,7 +46708,7 @@
         <v>46207</v>
       </c>
       <c r="C511" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D511" t="str">
         <v>Condones</v>
@@ -46731,7 +46731,7 @@
         <v>46209</v>
       </c>
       <c r="C512" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D512" t="str">
         <v>Madre</v>
@@ -46754,7 +46754,7 @@
         <v>46209</v>
       </c>
       <c r="C513" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D513" t="str">
         <v>Carol</v>
@@ -46777,7 +46777,7 @@
         <v>46209</v>
       </c>
       <c r="C514" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D514" t="str">
         <v>Taxi</v>
@@ -46800,7 +46800,7 @@
         <v>46209</v>
       </c>
       <c r="C515" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D515" t="str">
         <v>Apuestas</v>
@@ -46823,7 +46823,7 @@
         <v>46209</v>
       </c>
       <c r="C516" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D516" t="str">
         <v>Padre</v>
@@ -46846,7 +46846,7 @@
         <v>46210</v>
       </c>
       <c r="C517" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D517" t="str">
         <v>Utencilios de Limpieza</v>
@@ -46869,7 +46869,7 @@
         <v>46210</v>
       </c>
       <c r="C518" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D518" t="str">
         <v>Bus</v>
@@ -46892,7 +46892,7 @@
         <v>46211</v>
       </c>
       <c r="C519" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D519" t="str">
         <v>Broaster</v>
@@ -46915,7 +46915,7 @@
         <v>46213</v>
       </c>
       <c r="C520" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D520" t="str">
         <v>Carol</v>
@@ -46938,7 +46938,7 @@
         <v>46213</v>
       </c>
       <c r="C521" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D521" t="str">
         <v>Gratificación</v>
@@ -46961,7 +46961,7 @@
         <v>46213</v>
       </c>
       <c r="C522" t="str">
-        <v>Viajes &amp; Hospedaje</v>
+        <v>Gasto</v>
       </c>
       <c r="D522" t="str">
         <v>Viaje Brasil</v>
@@ -46984,7 +46984,7 @@
         <v>46213</v>
       </c>
       <c r="C523" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D523" t="str">
         <v>Titulación</v>
@@ -47007,7 +47007,7 @@
         <v>46213</v>
       </c>
       <c r="C524" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D524" t="str">
         <v>Desvagramen</v>
@@ -47030,7 +47030,7 @@
         <v>46214</v>
       </c>
       <c r="C525" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D525" t="str">
         <v>Taxi</v>
@@ -47053,7 +47053,7 @@
         <v>46214</v>
       </c>
       <c r="C526" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D526" t="str">
         <v>Alcohol</v>
@@ -47076,7 +47076,7 @@
         <v>46214</v>
       </c>
       <c r="C527" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D527" t="str">
         <v>Carol</v>
@@ -47099,7 +47099,7 @@
         <v>46214</v>
       </c>
       <c r="C528" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D528" t="str">
         <v>Crema de Manos</v>
@@ -47122,7 +47122,7 @@
         <v>46214</v>
       </c>
       <c r="C529" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D529" t="str">
         <v>Café</v>
@@ -47145,7 +47145,7 @@
         <v>46214</v>
       </c>
       <c r="C530" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D530" t="str">
         <v>Dollarcity</v>
@@ -47168,7 +47168,7 @@
         <v>46214</v>
       </c>
       <c r="C531" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D531" t="str">
         <v>Pizza</v>
@@ -47191,7 +47191,7 @@
         <v>46215</v>
       </c>
       <c r="C532" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D532" t="str">
         <v>Broaster</v>
@@ -47214,7 +47214,7 @@
         <v>46218</v>
       </c>
       <c r="C533" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D533" t="str">
         <v>Prestamo BCP</v>
@@ -47237,7 +47237,7 @@
         <v>46218</v>
       </c>
       <c r="C534" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Gasto</v>
       </c>
       <c r="D534" t="str">
         <v>Concierto Trueno</v>
@@ -47260,7 +47260,7 @@
         <v>46218</v>
       </c>
       <c r="C535" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D535" t="str">
         <v>Taxi</v>
@@ -47283,7 +47283,7 @@
         <v>46218</v>
       </c>
       <c r="C536" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D536" t="str">
         <v>Café</v>
@@ -47306,7 +47306,7 @@
         <v>46218</v>
       </c>
       <c r="C537" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D537" t="str">
         <v>Makis</v>
@@ -47329,7 +47329,7 @@
         <v>46218</v>
       </c>
       <c r="C538" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D538" t="str">
         <v>Carol</v>
@@ -47352,7 +47352,7 @@
         <v>46220</v>
       </c>
       <c r="C539" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D539" t="str">
         <v>Taxi</v>
@@ -47375,7 +47375,7 @@
         <v>46220</v>
       </c>
       <c r="C540" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D540" t="str">
         <v>Carol</v>
@@ -47398,7 +47398,7 @@
         <v>46221</v>
       </c>
       <c r="C541" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D541" t="str">
         <v>Taxi</v>
@@ -47421,7 +47421,7 @@
         <v>46221</v>
       </c>
       <c r="C542" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D542" t="str">
         <v>Shawarma</v>
@@ -47444,7 +47444,7 @@
         <v>46221</v>
       </c>
       <c r="C543" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D543" t="str">
         <v>Makis</v>
@@ -47467,7 +47467,7 @@
         <v>46222</v>
       </c>
       <c r="C544" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D544" t="str">
         <v>Ceviche</v>
@@ -47490,7 +47490,7 @@
         <v>46222</v>
       </c>
       <c r="C545" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D545" t="str">
         <v>Bus</v>
@@ -47513,7 +47513,7 @@
         <v>46222</v>
       </c>
       <c r="C546" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Gasto</v>
       </c>
       <c r="D546" t="str">
         <v>In Game</v>
@@ -47536,7 +47536,7 @@
         <v>46222</v>
       </c>
       <c r="C547" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D547" t="str">
         <v>Broaster</v>
@@ -47559,7 +47559,7 @@
         <v>46223</v>
       </c>
       <c r="C548" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D548" t="str">
         <v>Bus</v>
@@ -47582,7 +47582,7 @@
         <v>46223</v>
       </c>
       <c r="C549" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Gasto</v>
       </c>
       <c r="D549" t="str">
         <v>Minecraft</v>
@@ -47605,7 +47605,7 @@
         <v>46223</v>
       </c>
       <c r="C550" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D550" t="str">
         <v>Telefonia Movil</v>
@@ -47628,7 +47628,7 @@
         <v>46223</v>
       </c>
       <c r="C551" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D551" t="str">
         <v>Carol</v>
@@ -47651,7 +47651,7 @@
         <v>46223</v>
       </c>
       <c r="C552" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D552" t="str">
         <v>Broaster</v>
@@ -47674,7 +47674,7 @@
         <v>46226</v>
       </c>
       <c r="C553" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D553" t="str">
         <v>iCloud</v>
@@ -47697,7 +47697,7 @@
         <v>46226</v>
       </c>
       <c r="C554" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D554" t="str">
         <v>Taxi</v>
@@ -47720,7 +47720,7 @@
         <v>46226</v>
       </c>
       <c r="C555" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D555" t="str">
         <v>Agua Mineral</v>
@@ -47743,7 +47743,7 @@
         <v>46226</v>
       </c>
       <c r="C556" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D556" t="str">
         <v>Carol</v>
@@ -47766,7 +47766,7 @@
         <v>46226</v>
       </c>
       <c r="C557" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D557" t="str">
         <v>Makis</v>
@@ -47789,7 +47789,7 @@
         <v>46226</v>
       </c>
       <c r="C558" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D558" t="str">
         <v>Carol</v>
@@ -47812,7 +47812,7 @@
         <v>46227</v>
       </c>
       <c r="C559" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D559" t="str">
         <v>Gaseosa</v>
@@ -47835,7 +47835,7 @@
         <v>46227</v>
       </c>
       <c r="C560" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D560" t="str">
         <v>Futbol</v>
@@ -47858,7 +47858,7 @@
         <v>46228</v>
       </c>
       <c r="C561" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D561" t="str">
         <v>Taxi</v>
@@ -47881,7 +47881,7 @@
         <v>46228</v>
       </c>
       <c r="C562" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D562" t="str">
         <v>Taxi</v>
@@ -47904,7 +47904,7 @@
         <v>46228</v>
       </c>
       <c r="C563" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D563" t="str">
         <v>Pollo a la Brasa</v>
@@ -47927,7 +47927,7 @@
         <v>46229</v>
       </c>
       <c r="C564" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Gasto</v>
       </c>
       <c r="D564" t="str">
         <v>Skin de Valorant</v>
@@ -47950,7 +47950,7 @@
         <v>46229</v>
       </c>
       <c r="C565" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D565" t="str">
         <v>Broaster</v>
@@ -47973,7 +47973,7 @@
         <v>46230</v>
       </c>
       <c r="C566" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D566" t="str">
         <v>Bus</v>
@@ -47996,7 +47996,7 @@
         <v>46230</v>
       </c>
       <c r="C567" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D567" t="str">
         <v>Dulce</v>
@@ -48019,7 +48019,7 @@
         <v>46235</v>
       </c>
       <c r="C568" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D568" t="str">
         <v>Bonificación Ahorro</v>
@@ -48042,7 +48042,7 @@
         <v>46235</v>
       </c>
       <c r="C569" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D569" t="str">
         <v>Sueldo</v>
@@ -48065,7 +48065,7 @@
         <v>46235</v>
       </c>
       <c r="C570" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D570" t="str">
         <v>Linea Tarjeta</v>
@@ -48088,7 +48088,7 @@
         <v>46235</v>
       </c>
       <c r="C571" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D571" t="str">
         <v>Linea Tarjeta</v>
@@ -48111,7 +48111,7 @@
         <v>46235</v>
       </c>
       <c r="C572" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D572" t="str">
         <v>Linea Tarjeta</v>
@@ -48134,7 +48134,7 @@
         <v>46235</v>
       </c>
       <c r="C573" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D573" t="str">
         <v>Corte de Cabello</v>
@@ -48157,7 +48157,7 @@
         <v>46235</v>
       </c>
       <c r="C574" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D574" t="str">
         <v>iPhone 16</v>
@@ -48180,7 +48180,7 @@
         <v>46235</v>
       </c>
       <c r="C575" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D575" t="str">
         <v>Pago de Tarjeta Ripley</v>
@@ -48203,7 +48203,7 @@
         <v>46235</v>
       </c>
       <c r="C576" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D576" t="str">
         <v>Prestamo Yape</v>
@@ -48226,7 +48226,7 @@
         <v>46235</v>
       </c>
       <c r="C577" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D577" t="str">
         <v>Agua + Mantenimiento</v>
@@ -48249,7 +48249,7 @@
         <v>46235</v>
       </c>
       <c r="C578" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D578" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -48272,7 +48272,7 @@
         <v>46235</v>
       </c>
       <c r="C579" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D579" t="str">
         <v>Pago de Tarjeta BBVA Bfree</v>
@@ -48295,7 +48295,7 @@
         <v>46235</v>
       </c>
       <c r="C580" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D580" t="str">
         <v>Carol</v>
@@ -48318,7 +48318,7 @@
         <v>46235</v>
       </c>
       <c r="C581" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D581" t="str">
         <v>Carol</v>
@@ -48341,7 +48341,7 @@
         <v>46235</v>
       </c>
       <c r="C582" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D582" t="str">
         <v>Carol</v>
@@ -48364,7 +48364,7 @@
         <v>46235</v>
       </c>
       <c r="C583" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D583" t="str">
         <v>Carol</v>
@@ -48387,7 +48387,7 @@
         <v>46235</v>
       </c>
       <c r="C584" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D584" t="str">
         <v>Carol</v>
@@ -48410,7 +48410,7 @@
         <v>46235</v>
       </c>
       <c r="C585" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D585" t="str">
         <v>Taxi</v>
@@ -48433,7 +48433,7 @@
         <v>46235</v>
       </c>
       <c r="C586" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D586" t="str">
         <v>Utencilios de Limpieza</v>
@@ -48456,7 +48456,7 @@
         <v>46235</v>
       </c>
       <c r="C587" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D587" t="str">
         <v>Internet</v>
@@ -48479,7 +48479,7 @@
         <v>46235</v>
       </c>
       <c r="C588" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D588" t="str">
         <v>Bus</v>
@@ -48502,7 +48502,7 @@
         <v>46235</v>
       </c>
       <c r="C589" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D589" t="str">
         <v>Perfume Invictus</v>
@@ -48525,7 +48525,7 @@
         <v>46235</v>
       </c>
       <c r="C590" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D590" t="str">
         <v>Carol</v>
@@ -48548,7 +48548,7 @@
         <v>46235</v>
       </c>
       <c r="C591" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D591" t="str">
         <v>Café</v>
@@ -48571,7 +48571,7 @@
         <v>46235</v>
       </c>
       <c r="C592" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D592" t="str">
         <v>Gas</v>
@@ -48594,7 +48594,7 @@
         <v>46235</v>
       </c>
       <c r="C593" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D593" t="str">
         <v>Carol</v>
@@ -48617,7 +48617,7 @@
         <v>46235</v>
       </c>
       <c r="C594" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D594" t="str">
         <v>Gaseosa</v>
@@ -48640,7 +48640,7 @@
         <v>46235</v>
       </c>
       <c r="C595" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D595" t="str">
         <v>Mayonesa</v>
@@ -48663,7 +48663,7 @@
         <v>46235</v>
       </c>
       <c r="C596" t="str">
-        <v>Compras Generales &amp; Bazar</v>
+        <v>Gasto</v>
       </c>
       <c r="D596" t="str">
         <v>Poster de Spiderman</v>
@@ -48686,7 +48686,7 @@
         <v>46235</v>
       </c>
       <c r="C597" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D597" t="str">
         <v>Taxi</v>
@@ -48709,7 +48709,7 @@
         <v>46235</v>
       </c>
       <c r="C598" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D598" t="str">
         <v>Desvagramen</v>
@@ -48732,7 +48732,7 @@
         <v>46235</v>
       </c>
       <c r="C599" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D599" t="str">
         <v>Futbol</v>
@@ -48755,7 +48755,7 @@
         <v>46235</v>
       </c>
       <c r="C600" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D600" t="str">
         <v>Desvagramen</v>
@@ -48778,7 +48778,7 @@
         <v>46235</v>
       </c>
       <c r="C601" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D601" t="str">
         <v>Spotify</v>
@@ -48801,7 +48801,7 @@
         <v>46235</v>
       </c>
       <c r="C602" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D602" t="str">
         <v>Futbol</v>
@@ -48824,7 +48824,7 @@
         <v>46235</v>
       </c>
       <c r="C603" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D603" t="str">
         <v>Apuestas</v>
@@ -48847,7 +48847,7 @@
         <v>46236</v>
       </c>
       <c r="C604" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D604" t="str">
         <v>Taxi</v>
@@ -48870,7 +48870,7 @@
         <v>46236</v>
       </c>
       <c r="C605" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D605" t="str">
         <v>Utencilios de Limpieza</v>
@@ -48893,7 +48893,7 @@
         <v>46236</v>
       </c>
       <c r="C606" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D606" t="str">
         <v>Carol</v>
@@ -48916,7 +48916,7 @@
         <v>46236</v>
       </c>
       <c r="C607" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D607" t="str">
         <v>Carol</v>
@@ -48939,7 +48939,7 @@
         <v>46236</v>
       </c>
       <c r="C608" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D608" t="str">
         <v>Gaseosa</v>
@@ -48962,7 +48962,7 @@
         <v>46236</v>
       </c>
       <c r="C609" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D609" t="str">
         <v>Bus</v>
@@ -48985,7 +48985,7 @@
         <v>46237</v>
       </c>
       <c r="C610" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D610" t="str">
         <v>Ceviche</v>
@@ -49008,7 +49008,7 @@
         <v>46237</v>
       </c>
       <c r="C611" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D611" t="str">
         <v>Carol</v>
@@ -49031,7 +49031,7 @@
         <v>46237</v>
       </c>
       <c r="C612" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D612" t="str">
         <v>Taxi</v>
@@ -49054,7 +49054,7 @@
         <v>46238</v>
       </c>
       <c r="C613" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D613" t="str">
         <v>Bus</v>
@@ -49077,7 +49077,7 @@
         <v>46238</v>
       </c>
       <c r="C614" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D614" t="str">
         <v>Broaster</v>
@@ -49100,7 +49100,7 @@
         <v>46239</v>
       </c>
       <c r="C615" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D615" t="str">
         <v>Taxi</v>
@@ -49123,7 +49123,7 @@
         <v>46239</v>
       </c>
       <c r="C616" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D616" t="str">
         <v>Carol</v>
@@ -49146,7 +49146,7 @@
         <v>46239</v>
       </c>
       <c r="C617" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D617" t="str">
         <v>Carol</v>
@@ -49169,7 +49169,7 @@
         <v>46240</v>
       </c>
       <c r="C618" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D618" t="str">
         <v>Taxi</v>
@@ -49192,7 +49192,7 @@
         <v>46240</v>
       </c>
       <c r="C619" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D619" t="str">
         <v>Ceviche</v>
@@ -49215,7 +49215,7 @@
         <v>46241</v>
       </c>
       <c r="C620" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D620" t="str">
         <v>Desvagramen</v>
@@ -49238,7 +49238,7 @@
         <v>46241</v>
       </c>
       <c r="C621" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D621" t="str">
         <v>Futbol</v>
@@ -49261,7 +49261,7 @@
         <v>46242</v>
       </c>
       <c r="C622" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D622" t="str">
         <v>Broaster</v>
@@ -49284,7 +49284,7 @@
         <v>46242</v>
       </c>
       <c r="C623" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D623" t="str">
         <v>Futbol</v>
@@ -49307,7 +49307,7 @@
         <v>46243</v>
       </c>
       <c r="C624" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D624" t="str">
         <v>Carol</v>
@@ -49330,7 +49330,7 @@
         <v>46243</v>
       </c>
       <c r="C625" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D625" t="str">
         <v>Taxi</v>
@@ -49353,7 +49353,7 @@
         <v>46243</v>
       </c>
       <c r="C626" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D626" t="str">
         <v>Carol</v>
@@ -49376,7 +49376,7 @@
         <v>46243</v>
       </c>
       <c r="C627" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D627" t="str">
         <v>Chifa</v>
@@ -49399,7 +49399,7 @@
         <v>46243</v>
       </c>
       <c r="C628" t="str">
-        <v>Salud &amp; Farmacia</v>
+        <v>Gasto</v>
       </c>
       <c r="D628" t="str">
         <v>Medicina Madre</v>
@@ -49422,7 +49422,7 @@
         <v>46243</v>
       </c>
       <c r="C629" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D629" t="str">
         <v>Madre</v>
@@ -49445,7 +49445,7 @@
         <v>46243</v>
       </c>
       <c r="C630" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Gasto</v>
       </c>
       <c r="D630" t="str">
         <v>Desvagramen</v>
@@ -49468,7 +49468,7 @@
         <v>46244</v>
       </c>
       <c r="C631" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D631" t="str">
         <v>Taxi</v>
@@ -49491,7 +49491,7 @@
         <v>46244</v>
       </c>
       <c r="C632" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D632" t="str">
         <v>Carol</v>
@@ -49514,7 +49514,7 @@
         <v>46245</v>
       </c>
       <c r="C633" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D633" t="str">
         <v>Luz</v>
@@ -49537,7 +49537,7 @@
         <v>46245</v>
       </c>
       <c r="C634" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D634" t="str">
         <v>Telefonia Movil</v>
@@ -49560,7 +49560,7 @@
         <v>46245</v>
       </c>
       <c r="C635" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D635" t="str">
         <v>Apuestas</v>
@@ -49583,7 +49583,7 @@
         <v>46245</v>
       </c>
       <c r="C636" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D636" t="str">
         <v>Broaster</v>
@@ -49606,7 +49606,7 @@
         <v>46246</v>
       </c>
       <c r="C637" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D637" t="str">
         <v>Carol</v>
@@ -49629,7 +49629,7 @@
         <v>46246</v>
       </c>
       <c r="C638" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D638" t="str">
         <v>Gaseosa</v>
@@ -49652,7 +49652,7 @@
         <v>46246</v>
       </c>
       <c r="C639" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D639" t="str">
         <v>Carol</v>
@@ -49675,7 +49675,7 @@
         <v>46246</v>
       </c>
       <c r="C640" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D640" t="str">
         <v>Planet Chicken</v>
@@ -49698,7 +49698,7 @@
         <v>46246</v>
       </c>
       <c r="C641" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D641" t="str">
         <v>Bus</v>
@@ -49721,7 +49721,7 @@
         <v>46246</v>
       </c>
       <c r="C642" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D642" t="str">
         <v>Bus</v>
@@ -49744,7 +49744,7 @@
         <v>46246</v>
       </c>
       <c r="C643" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D643" t="str">
         <v>Broaster</v>
@@ -49767,7 +49767,7 @@
         <v>46246</v>
       </c>
       <c r="C644" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D644" t="str">
         <v>Bus</v>
@@ -49790,7 +49790,7 @@
         <v>46247</v>
       </c>
       <c r="C645" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D645" t="str">
         <v>Bus</v>
@@ -49813,7 +49813,7 @@
         <v>46247</v>
       </c>
       <c r="C646" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Gasto</v>
       </c>
       <c r="D646" t="str">
         <v>Carol</v>
@@ -49836,7 +49836,7 @@
         <v>46247</v>
       </c>
       <c r="C647" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D647" t="str">
         <v>Taxi</v>
@@ -49859,7 +49859,7 @@
         <v>46247</v>
       </c>
       <c r="C648" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D648" t="str">
         <v>Bus</v>
@@ -49882,7 +49882,7 @@
         <v>46247</v>
       </c>
       <c r="C649" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D649" t="str">
         <v>Gaseosa</v>
@@ -49905,7 +49905,7 @@
         <v>46247</v>
       </c>
       <c r="C650" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D650" t="str">
         <v>Makis</v>
@@ -49928,7 +49928,7 @@
         <v>46248</v>
       </c>
       <c r="C651" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D651" t="str">
         <v>Bus</v>
@@ -49951,7 +49951,7 @@
         <v>46248</v>
       </c>
       <c r="C652" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D652" t="str">
         <v>Futbol</v>
@@ -49974,7 +49974,7 @@
         <v>46249</v>
       </c>
       <c r="C653" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D653" t="str">
         <v>Prestamo BCP</v>
@@ -49997,7 +49997,7 @@
         <v>46249</v>
       </c>
       <c r="C654" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D654" t="str">
         <v>Gaseosa</v>
@@ -50020,7 +50020,7 @@
         <v>46249</v>
       </c>
       <c r="C655" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D655" t="str">
         <v>Broaster</v>
@@ -50043,7 +50043,7 @@
         <v>46249</v>
       </c>
       <c r="C656" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D656" t="str">
         <v>Taxi</v>
@@ -50066,7 +50066,7 @@
         <v>46249</v>
       </c>
       <c r="C657" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D657" t="str">
         <v>Alcohol</v>
@@ -50089,7 +50089,7 @@
         <v>46250</v>
       </c>
       <c r="C658" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D658" t="str">
         <v>Broaster</v>
@@ -50112,7 +50112,7 @@
         <v>46251</v>
       </c>
       <c r="C659" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D659" t="str">
         <v>Utencilios de Limpieza</v>
@@ -50135,7 +50135,7 @@
         <v>46251</v>
       </c>
       <c r="C660" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D660" t="str">
         <v>Gaseosa</v>
@@ -50158,7 +50158,7 @@
         <v>46252</v>
       </c>
       <c r="C661" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D661" t="str">
         <v>Broaster</v>
@@ -50181,7 +50181,7 @@
         <v>46253</v>
       </c>
       <c r="C662" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D662" t="str">
         <v>Broaster</v>
@@ -50204,7 +50204,7 @@
         <v>46254</v>
       </c>
       <c r="C663" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D663" t="str">
         <v>Gaseosa</v>
@@ -50227,7 +50227,7 @@
         <v>46255</v>
       </c>
       <c r="C664" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D664" t="str">
         <v>Broaster</v>
@@ -50250,7 +50250,7 @@
         <v>46255</v>
       </c>
       <c r="C665" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D665" t="str">
         <v>Futbol</v>
@@ -50273,7 +50273,7 @@
         <v>46256</v>
       </c>
       <c r="C666" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D666" t="str">
         <v>Futbol</v>
@@ -50296,7 +50296,7 @@
         <v>46256</v>
       </c>
       <c r="C667" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D667" t="str">
         <v>Broaster</v>
@@ -50319,7 +50319,7 @@
         <v>46257</v>
       </c>
       <c r="C668" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D668" t="str">
         <v>iCloud</v>
@@ -50342,7 +50342,7 @@
         <v>46257</v>
       </c>
       <c r="C669" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D669" t="str">
         <v>Pollo a la Brasa</v>
@@ -50365,7 +50365,7 @@
         <v>46257</v>
       </c>
       <c r="C670" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D670" t="str">
         <v>Taxi</v>
@@ -50388,7 +50388,7 @@
         <v>46258</v>
       </c>
       <c r="C671" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D671" t="str">
         <v>Shawarma</v>
@@ -50411,7 +50411,7 @@
         <v>46258</v>
       </c>
       <c r="C672" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D672" t="str">
         <v>Utencilios de Limpieza</v>
@@ -50434,7 +50434,7 @@
         <v>46261</v>
       </c>
       <c r="C673" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D673" t="str">
         <v>Utencilios de Limpieza</v>
@@ -50457,7 +50457,7 @@
         <v>46261</v>
       </c>
       <c r="C674" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D674" t="str">
         <v>Broaster</v>
@@ -50480,7 +50480,7 @@
         <v>46261</v>
       </c>
       <c r="C675" t="str">
-        <v>Conciertos &amp; Eventos</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D675" t="str">
         <v>Entrada Paulo Londra</v>
@@ -50503,7 +50503,7 @@
         <v>46266</v>
       </c>
       <c r="C676" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D676" t="str">
         <v>Bus</v>
@@ -50526,7 +50526,7 @@
         <v>46266</v>
       </c>
       <c r="C677" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D677" t="str">
         <v>Gas</v>
@@ -50549,7 +50549,7 @@
         <v>46266</v>
       </c>
       <c r="C678" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D678" t="str">
         <v>Internet</v>
@@ -50572,7 +50572,7 @@
         <v>46266</v>
       </c>
       <c r="C679" t="str">
-        <v>Entretenimiento &amp; Streaming</v>
+        <v>Servicio</v>
       </c>
       <c r="D679" t="str">
         <v>Spotify</v>
@@ -50595,7 +50595,7 @@
         <v>46266</v>
       </c>
       <c r="C680" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D680" t="str">
         <v>Pollo a la Brasa</v>
@@ -50618,7 +50618,7 @@
         <v>46266</v>
       </c>
       <c r="C681" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D681" t="str">
         <v>Apuestas</v>
@@ -50641,7 +50641,7 @@
         <v>46266</v>
       </c>
       <c r="C682" t="str">
-        <v>Otros Ingresos &amp; Ventas</v>
+        <v>Otro Ing</v>
       </c>
       <c r="D682" t="str">
         <v>Bonificación Ahorro</v>
@@ -50664,7 +50664,7 @@
         <v>46266</v>
       </c>
       <c r="C683" t="str">
-        <v>Sueldos &amp; Beneficios Laborales</v>
+        <v>Sueldo</v>
       </c>
       <c r="D683" t="str">
         <v>Sueldo</v>
@@ -50687,7 +50687,7 @@
         <v>46266</v>
       </c>
       <c r="C684" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D684" t="str">
         <v>Linea Tarjeta</v>
@@ -50710,7 +50710,7 @@
         <v>46266</v>
       </c>
       <c r="C685" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D685" t="str">
         <v>Linea Tarjeta</v>
@@ -50733,7 +50733,7 @@
         <v>46266</v>
       </c>
       <c r="C686" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Tarjeta</v>
       </c>
       <c r="D686" t="str">
         <v>Linea Tarjeta</v>
@@ -50756,7 +50756,7 @@
         <v>46266</v>
       </c>
       <c r="C687" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D687" t="str">
         <v>Pago de Tarjeta Ripley</v>
@@ -50779,7 +50779,7 @@
         <v>46266</v>
       </c>
       <c r="C688" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D688" t="str">
         <v>Prestamo Yape</v>
@@ -50802,7 +50802,7 @@
         <v>46266</v>
       </c>
       <c r="C689" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D689" t="str">
         <v>Corte de Cabello</v>
@@ -50825,7 +50825,7 @@
         <v>46266</v>
       </c>
       <c r="C690" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D690" t="str">
         <v>iPhone 16</v>
@@ -50848,7 +50848,7 @@
         <v>46266</v>
       </c>
       <c r="C691" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D691" t="str">
         <v>Futbol</v>
@@ -50871,7 +50871,7 @@
         <v>46266</v>
       </c>
       <c r="C692" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D692" t="str">
         <v>IA</v>
@@ -50894,7 +50894,7 @@
         <v>46266</v>
       </c>
       <c r="C693" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D693" t="str">
         <v>Gaseosa</v>
@@ -50917,7 +50917,7 @@
         <v>46266</v>
       </c>
       <c r="C694" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D694" t="str">
         <v>Tortes</v>
@@ -50940,7 +50940,7 @@
         <v>46266</v>
       </c>
       <c r="C695" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D695" t="str">
         <v>Futbol</v>
@@ -50963,7 +50963,7 @@
         <v>46266</v>
       </c>
       <c r="C696" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D696" t="str">
         <v>Broaster</v>
@@ -50986,7 +50986,7 @@
         <v>46266</v>
       </c>
       <c r="C697" t="str">
-        <v>Salidas &amp; Sociales</v>
+        <v>Gasto</v>
       </c>
       <c r="D697" t="str">
         <v>Alcohol</v>
@@ -51009,7 +51009,7 @@
         <v>46266</v>
       </c>
       <c r="C698" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D698" t="str">
         <v>Ceviche</v>
@@ -51032,7 +51032,7 @@
         <v>46266</v>
       </c>
       <c r="C699" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D699" t="str">
         <v>Café</v>
@@ -51055,7 +51055,7 @@
         <v>46266</v>
       </c>
       <c r="C700" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D700" t="str">
         <v>Bus</v>
@@ -51078,7 +51078,7 @@
         <v>46266</v>
       </c>
       <c r="C701" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D701" t="str">
         <v>Agua Mineral</v>
@@ -51101,7 +51101,7 @@
         <v>46266</v>
       </c>
       <c r="C702" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D702" t="str">
         <v>Gaseosa</v>
@@ -51124,7 +51124,7 @@
         <v>46266</v>
       </c>
       <c r="C703" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D703" t="str">
         <v>Bus</v>
@@ -51147,7 +51147,7 @@
         <v>46266</v>
       </c>
       <c r="C704" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D704" t="str">
         <v>Bus</v>
@@ -51170,7 +51170,7 @@
         <v>46266</v>
       </c>
       <c r="C705" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Servicio</v>
       </c>
       <c r="D705" t="str">
         <v>Gaseosa</v>
@@ -51193,7 +51193,7 @@
         <v>46266</v>
       </c>
       <c r="C706" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D706" t="str">
         <v>Pago de Tarjeta Interbank Amex</v>
@@ -51216,7 +51216,7 @@
         <v>46266</v>
       </c>
       <c r="C707" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D707" t="str">
         <v>Pago de Tarjeta BBVA Bfree</v>
@@ -51239,7 +51239,7 @@
         <v>46266</v>
       </c>
       <c r="C708" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D708" t="str">
         <v>Agua + Mantenimiento</v>
@@ -51262,7 +51262,7 @@
         <v>46267</v>
       </c>
       <c r="C709" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D709" t="str">
         <v>Bus</v>
@@ -51285,7 +51285,7 @@
         <v>46267</v>
       </c>
       <c r="C710" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D710" t="str">
         <v>Makis</v>
@@ -51308,7 +51308,7 @@
         <v>46267</v>
       </c>
       <c r="C711" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D711" t="str">
         <v>Bus</v>
@@ -51331,7 +51331,7 @@
         <v>46268</v>
       </c>
       <c r="C712" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Servicio</v>
       </c>
       <c r="D712" t="str">
         <v>Desvagramen</v>
@@ -51354,7 +51354,7 @@
         <v>46269</v>
       </c>
       <c r="C713" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D713" t="str">
         <v>Cine</v>
@@ -51377,7 +51377,7 @@
         <v>46269</v>
       </c>
       <c r="C714" t="str">
-        <v>Cuidado Personal &amp; Aseo</v>
+        <v>Gasto</v>
       </c>
       <c r="D714" t="str">
         <v>Pasta Dental</v>
@@ -51400,7 +51400,7 @@
         <v>46269</v>
       </c>
       <c r="C715" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D715" t="str">
         <v>Bus</v>
@@ -51423,7 +51423,7 @@
         <v>46269</v>
       </c>
       <c r="C716" t="str">
-        <v>Familia &amp; Transferencias</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D716" t="str">
         <v>Carol</v>
@@ -51446,7 +51446,7 @@
         <v>46269</v>
       </c>
       <c r="C717" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D717" t="str">
         <v>Mayonesa</v>
@@ -51469,7 +51469,7 @@
         <v>46269</v>
       </c>
       <c r="C718" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D718" t="str">
         <v>Gaseosa</v>
@@ -51492,7 +51492,7 @@
         <v>46269</v>
       </c>
       <c r="C719" t="str">
-        <v>Gustos &amp; Ocio</v>
+        <v>Gasto</v>
       </c>
       <c r="D719" t="str">
         <v>Futbol</v>
@@ -51515,7 +51515,7 @@
         <v>46269</v>
       </c>
       <c r="C720" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D720" t="str">
         <v>Gaseosa</v>
@@ -51538,7 +51538,7 @@
         <v>46269</v>
       </c>
       <c r="C721" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D721" t="str">
         <v>Taxi</v>
@@ -51561,7 +51561,7 @@
         <v>46270</v>
       </c>
       <c r="C722" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D722" t="str">
         <v>Broaster</v>
@@ -51584,7 +51584,7 @@
         <v>46270</v>
       </c>
       <c r="C723" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D723" t="str">
         <v>Galleta</v>
@@ -51607,7 +51607,7 @@
         <v>46270</v>
       </c>
       <c r="C724" t="str">
-        <v>Hogar &amp; Mantenimiento</v>
+        <v>Gasto</v>
       </c>
       <c r="D724" t="str">
         <v>Detergente</v>
@@ -51630,7 +51630,7 @@
         <v>46270</v>
       </c>
       <c r="C725" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D725" t="str">
         <v>Bus</v>
@@ -51653,7 +51653,7 @@
         <v>46270</v>
       </c>
       <c r="C726" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D726" t="str">
         <v>Makis</v>
@@ -51676,7 +51676,7 @@
         <v>46270</v>
       </c>
       <c r="C727" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D727" t="str">
         <v>Bus</v>
@@ -51699,7 +51699,7 @@
         <v>46271</v>
       </c>
       <c r="C728" t="str">
-        <v>Supermercado &amp; Alimentos</v>
+        <v>Gasto</v>
       </c>
       <c r="D728" t="str">
         <v>Gaseosa</v>
@@ -51722,7 +51722,7 @@
         <v>46271</v>
       </c>
       <c r="C729" t="str">
-        <v>Ropa &amp; Calzado</v>
+        <v>Gasto</v>
       </c>
       <c r="D729" t="str">
         <v>Casaca</v>
@@ -51745,7 +51745,7 @@
         <v>46271</v>
       </c>
       <c r="C730" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D730" t="str">
         <v>Bus</v>
@@ -51768,7 +51768,7 @@
         <v>46271</v>
       </c>
       <c r="C731" t="str">
-        <v>Comida &amp; Restaurantes</v>
+        <v>Gasto</v>
       </c>
       <c r="D731" t="str">
         <v>Pollo a la Brasa</v>
@@ -51791,7 +51791,7 @@
         <v>46271</v>
       </c>
       <c r="C732" t="str">
-        <v>Tecnología &amp; Gadgets</v>
+        <v>Gasto</v>
       </c>
       <c r="D732" t="str">
         <v>Case</v>
@@ -51814,7 +51814,7 @@
         <v>46271</v>
       </c>
       <c r="C733" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D733" t="str">
         <v>Bus</v>
@@ -51837,7 +51837,7 @@
         <v>46272</v>
       </c>
       <c r="C734" t="str">
-        <v>Transporte &amp; Movilidad</v>
+        <v>Gasto</v>
       </c>
       <c r="D734" t="str">
         <v>Bus</v>
@@ -51860,7 +51860,7 @@
         <v>46280</v>
       </c>
       <c r="C735" t="str">
-        <v>Trámites &amp; Documentos</v>
+        <v>Otro Egre</v>
       </c>
       <c r="D735" t="str">
         <v>Titulación</v>
@@ -51883,7 +51883,7 @@
         <v>46280</v>
       </c>
       <c r="C736" t="str">
-        <v>Pagos de Tarjetas &amp; Deudas</v>
+        <v>Deuda</v>
       </c>
       <c r="D736" t="str">
         <v>Prestamo BCP</v>
@@ -51906,7 +51906,7 @@
         <v>46288</v>
       </c>
       <c r="C737" t="str">
-        <v>Servicios Básicos &amp; Facturas</v>
+        <v>Servicio</v>
       </c>
       <c r="D737" t="str">
         <v>iCloud</v>

--- a/Finanzas Personales.xlsx
+++ b/Finanzas Personales.xlsx
@@ -170,10 +170,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -205,10 +205,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -6348,10 +6348,10 @@
         <v>46059</v>
       </c>
       <c r="C119" t="str">
-        <v>Otro Ing</v>
+        <v>Sueldo</v>
       </c>
       <c r="D119" t="str">
-        <v>Viaje Argentina</v>
+        <v>AFP</v>
       </c>
       <c r="E119">
         <v>600</v>
@@ -31822,6 +31822,24 @@
       </c>
       <c r="G740" t="str">
         <v>Marzo</v>
+      </c>
+      <c r="H740" t="str">
+        <v/>
+      </c>
+      <c r="I740" t="str">
+        <v/>
+      </c>
+      <c r="J740" t="str">
+        <v/>
+      </c>
+      <c r="K740" t="str">
+        <v/>
+      </c>
+      <c r="L740" t="str">
+        <v/>
+      </c>
+      <c r="M740" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -34557,10 +34575,10 @@
         <v>46059</v>
       </c>
       <c r="C119" t="str">
-        <v>Otro Ing</v>
+        <v>Sueldo</v>
       </c>
       <c r="D119" t="str">
-        <v>Viaje Argentina</v>
+        <v>AFP</v>
       </c>
       <c r="E119">
         <v>600</v>
